--- a/outputs/views_single_sheet.xlsx
+++ b/outputs/views_single_sheet.xlsx
@@ -1984,7 +1984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI258"/>
+  <dimension ref="A1:BU258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,30 +2001,33 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C3" t="n">
         <v>2016</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>2017</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>2018</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>2019</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>2020</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2021</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2022</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2023</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -2035,30 +2038,33 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>131674079</v>
+      </c>
+      <c r="C4" t="n">
         <v>135479317</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>141138467</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>145589880</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>149817309</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>72541993</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>71772542</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>124601264</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>141225234</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>146236303</v>
       </c>
     </row>
@@ -2069,30 +2075,33 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>93216968</v>
+      </c>
+      <c r="C5" t="n">
         <v>99840032</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>103787168</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>105311465</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>108716046</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>34589072</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>60724131</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>102882568</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>111991774</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>116166159</v>
       </c>
     </row>
@@ -2103,30 +2112,33 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>113893218</v>
+      </c>
+      <c r="C6" t="n">
         <v>113894796</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>119358404</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>121347730</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>123427258</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>59668239</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>77227709</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>115313668</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>120732180</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>120181637</v>
       </c>
     </row>
@@ -2149,15 +2161,18 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D12" t="n">
         <v>2021</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>2022</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>2023</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -2169,19 +2184,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AFR</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C13" t="n">
+        <v>66919</v>
+      </c>
+      <c r="D13" t="n">
         <v>56454</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>178585</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>211797</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>228564</v>
       </c>
     </row>
@@ -2193,20 +2211,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AFR_OTH</t>
+          <t>All countries of the world</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>48888</v>
+        <v>72541993</v>
       </c>
       <c r="D14" t="n">
-        <v>137254</v>
+        <v>71772542</v>
       </c>
       <c r="E14" t="n">
-        <v>164179</v>
+        <v>124601264</v>
       </c>
       <c r="F14" t="n">
-        <v>182129</v>
+        <v>141225234</v>
+      </c>
+      <c r="G14" t="n">
+        <v>146236303</v>
       </c>
     </row>
     <row r="15">
@@ -2217,19 +2238,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>America</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>747934</v>
+      </c>
+      <c r="D15" t="n">
         <v>829600</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>2855684</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>3568735</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>3997581</v>
       </c>
     </row>
@@ -2241,20 +2265,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AME_C_S</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>96014</v>
+        <v>682011</v>
       </c>
       <c r="D16" t="n">
-        <v>444671</v>
+        <v>534055</v>
       </c>
       <c r="E16" t="n">
-        <v>561176</v>
+        <v>1672195</v>
       </c>
       <c r="F16" t="n">
-        <v>612203</v>
+        <v>2708963</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3100658</v>
       </c>
     </row>
     <row r="17">
@@ -2265,20 +2292,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AME_C_S_OTH</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>68364</v>
+        <v>40852</v>
       </c>
       <c r="D17" t="n">
-        <v>275453</v>
+        <v>16220</v>
       </c>
       <c r="E17" t="n">
-        <v>346603</v>
+        <v>161126</v>
       </c>
       <c r="F17" t="n">
-        <v>379229</v>
+        <v>290258</v>
+      </c>
+      <c r="G17" t="n">
+        <v>292028</v>
       </c>
     </row>
     <row r="18">
@@ -2289,20 +2319,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AME_N</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>733586</v>
+        <v>751324</v>
       </c>
       <c r="D18" t="n">
-        <v>2411013</v>
+        <v>768015</v>
       </c>
       <c r="E18" t="n">
-        <v>3007559</v>
+        <v>1553230</v>
       </c>
       <c r="F18" t="n">
-        <v>3385378</v>
+        <v>1808448</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1914604</v>
       </c>
     </row>
     <row r="19">
@@ -2313,20 +2346,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AME_N_OTH</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4221</v>
+        <v>467762</v>
       </c>
       <c r="D19" t="n">
-        <v>19743</v>
+        <v>514316</v>
       </c>
       <c r="E19" t="n">
-        <v>28272</v>
+        <v>995939</v>
       </c>
       <c r="F19" t="n">
-        <v>32043</v>
+        <v>1149304</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1214403</v>
       </c>
     </row>
     <row r="20">
@@ -2337,20 +2373,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASI</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>534055</v>
+        <v>50004</v>
       </c>
       <c r="D20" t="n">
-        <v>1672195</v>
+        <v>27650</v>
       </c>
       <c r="E20" t="n">
-        <v>2708963</v>
+        <v>169218</v>
       </c>
       <c r="F20" t="n">
-        <v>3100658</v>
+        <v>214573</v>
+      </c>
+      <c r="G20" t="n">
+        <v>232974</v>
       </c>
     </row>
     <row r="21">
@@ -2361,20 +2400,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASI_OTH</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>430511</v>
+        <v>49949</v>
       </c>
       <c r="D21" t="n">
-        <v>1267391</v>
+        <v>51580</v>
       </c>
       <c r="E21" t="n">
-        <v>1679369</v>
+        <v>95122</v>
       </c>
       <c r="F21" t="n">
-        <v>1763293</v>
+        <v>124571</v>
+      </c>
+      <c r="G21" t="n">
+        <v>133415</v>
       </c>
     </row>
     <row r="22">
@@ -2385,20 +2427,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>768015</v>
+        <v>57655</v>
       </c>
       <c r="D22" t="n">
-        <v>1553230</v>
+        <v>55613</v>
       </c>
       <c r="E22" t="n">
-        <v>1808448</v>
+        <v>188936</v>
       </c>
       <c r="F22" t="n">
-        <v>1914604</v>
+        <v>250090</v>
+      </c>
+      <c r="G22" t="n">
+        <v>275564</v>
       </c>
     </row>
     <row r="23">
@@ -2409,20 +2454,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Central and South America</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16220</v>
+        <v>116872</v>
       </c>
       <c r="D23" t="n">
-        <v>161126</v>
+        <v>96014</v>
       </c>
       <c r="E23" t="n">
-        <v>290258</v>
+        <v>444671</v>
       </c>
       <c r="F23" t="n">
-        <v>292028</v>
+        <v>561176</v>
+      </c>
+      <c r="G23" t="n">
+        <v>612203</v>
       </c>
     </row>
     <row r="24">
@@ -2433,20 +2481,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>514316</v>
+        <v>151734</v>
       </c>
       <c r="D24" t="n">
-        <v>995939</v>
+        <v>51770</v>
       </c>
       <c r="E24" t="n">
-        <v>1149304</v>
+        <v>168311</v>
       </c>
       <c r="F24" t="n">
-        <v>1214403</v>
+        <v>557123</v>
+      </c>
+      <c r="G24" t="n">
+        <v>808113</v>
       </c>
     </row>
     <row r="25">
@@ -2457,20 +2508,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>51580</v>
+        <v>50909</v>
       </c>
       <c r="D25" t="n">
-        <v>95122</v>
+        <v>52081</v>
       </c>
       <c r="E25" t="n">
-        <v>124571</v>
+        <v>98962</v>
       </c>
       <c r="F25" t="n">
-        <v>133415</v>
+        <v>131684</v>
+      </c>
+      <c r="G25" t="n">
+        <v>147406</v>
       </c>
     </row>
     <row r="26">
@@ -2481,20 +2535,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27650</v>
+        <v>8132</v>
       </c>
       <c r="D26" t="n">
-        <v>169218</v>
+        <v>8501</v>
       </c>
       <c r="E26" t="n">
-        <v>214573</v>
+        <v>20759</v>
       </c>
       <c r="F26" t="n">
-        <v>232974</v>
+        <v>28284</v>
+      </c>
+      <c r="G26" t="n">
+        <v>33682</v>
       </c>
     </row>
     <row r="27">
@@ -2505,20 +2562,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>55613</v>
+        <v>180860</v>
       </c>
       <c r="D27" t="n">
-        <v>188936</v>
+        <v>192119</v>
       </c>
       <c r="E27" t="n">
-        <v>250090</v>
+        <v>421978</v>
       </c>
       <c r="F27" t="n">
-        <v>275564</v>
+        <v>513932</v>
+      </c>
+      <c r="G27" t="n">
+        <v>530388</v>
       </c>
     </row>
     <row r="28">
@@ -2529,20 +2589,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CH_LI</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1037436</v>
+        <v>577700</v>
       </c>
       <c r="D28" t="n">
-        <v>2333054</v>
+        <v>610074</v>
       </c>
       <c r="E28" t="n">
-        <v>2710198</v>
+        <v>1132264</v>
       </c>
       <c r="F28" t="n">
-        <v>2785975</v>
+        <v>1236198</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1271529</v>
       </c>
     </row>
     <row r="29">
@@ -2553,20 +2616,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>Domestic country</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>51770</v>
+        <v>61923485</v>
       </c>
       <c r="D29" t="n">
-        <v>168311</v>
+        <v>61620107</v>
       </c>
       <c r="E29" t="n">
-        <v>557123</v>
+        <v>100062034</v>
       </c>
       <c r="F29" t="n">
-        <v>808113</v>
+        <v>111203933</v>
+      </c>
+      <c r="G29" t="n">
+        <v>113894811</v>
       </c>
     </row>
     <row r="30">
@@ -2577,20 +2643,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>EU27 countries (from 2020) except reporting country</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8501</v>
+        <v>6434483</v>
       </c>
       <c r="D30" t="n">
-        <v>20759</v>
+        <v>6638884</v>
       </c>
       <c r="E30" t="n">
-        <v>28284</v>
+        <v>14115497</v>
       </c>
       <c r="F30" t="n">
-        <v>33682</v>
+        <v>16354099</v>
+      </c>
+      <c r="G30" t="n">
+        <v>17264800</v>
       </c>
     </row>
     <row r="31">
@@ -2601,20 +2670,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>192119</v>
+        <v>20736</v>
       </c>
       <c r="D31" t="n">
-        <v>421978</v>
+        <v>22748</v>
       </c>
       <c r="E31" t="n">
-        <v>513932</v>
+        <v>50038</v>
       </c>
       <c r="F31" t="n">
-        <v>530388</v>
+        <v>60330</v>
+      </c>
+      <c r="G31" t="n">
+        <v>67144</v>
       </c>
     </row>
     <row r="32">
@@ -2625,20 +2697,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>61620107</v>
+        <v>70754047</v>
       </c>
       <c r="D32" t="n">
-        <v>100062034</v>
+        <v>70157831</v>
       </c>
       <c r="E32" t="n">
-        <v>111203933</v>
+        <v>119325095</v>
       </c>
       <c r="F32" t="n">
-        <v>113894811</v>
+        <v>133831926</v>
+      </c>
+      <c r="G32" t="n">
+        <v>137854964</v>
       </c>
     </row>
     <row r="33">
@@ -2649,20 +2724,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>European Free Trade Association</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>610074</v>
+        <v>1261598</v>
       </c>
       <c r="D33" t="n">
-        <v>1132264</v>
+        <v>1123527</v>
       </c>
       <c r="E33" t="n">
-        <v>1236198</v>
+        <v>2647337</v>
       </c>
       <c r="F33" t="n">
-        <v>1271529</v>
+        <v>3038844</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3121904</v>
       </c>
     </row>
     <row r="34">
@@ -2673,20 +2751,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>61620107</v>
+        <v>64558</v>
       </c>
       <c r="D34" t="n">
-        <v>100062034</v>
+        <v>58682</v>
       </c>
       <c r="E34" t="n">
-        <v>111203933</v>
+        <v>202214</v>
       </c>
       <c r="F34" t="n">
-        <v>113894811</v>
+        <v>231309</v>
+      </c>
+      <c r="G34" t="n">
+        <v>235040</v>
       </c>
     </row>
     <row r="35">
@@ -2697,20 +2778,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>22748</v>
+        <v>583949</v>
       </c>
       <c r="D35" t="n">
-        <v>50038</v>
+        <v>621147</v>
       </c>
       <c r="E35" t="n">
-        <v>60330</v>
+        <v>1322409</v>
       </c>
       <c r="F35" t="n">
-        <v>67144</v>
+        <v>1524189</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1590854</v>
       </c>
     </row>
     <row r="36">
@@ -2721,20 +2805,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EFTA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1123527</v>
+        <v>61923485</v>
       </c>
       <c r="D36" t="n">
-        <v>2647337</v>
+        <v>61620107</v>
       </c>
       <c r="E36" t="n">
-        <v>3038844</v>
+        <v>100062034</v>
       </c>
       <c r="F36" t="n">
-        <v>3121904</v>
+        <v>111203933</v>
+      </c>
+      <c r="G36" t="n">
+        <v>113894811</v>
       </c>
     </row>
     <row r="37">
@@ -2745,19 +2832,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>55359</v>
+      </c>
+      <c r="D37" t="n">
         <v>57259</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>123986</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>156577</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>183789</v>
       </c>
     </row>
@@ -2769,20 +2859,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>312331</v>
+        <v>85798</v>
       </c>
       <c r="D38" t="n">
-        <v>802411</v>
+        <v>86566</v>
       </c>
       <c r="E38" t="n">
-        <v>934579</v>
+        <v>181664</v>
       </c>
       <c r="F38" t="n">
-        <v>989197</v>
+        <v>228553</v>
+      </c>
+      <c r="G38" t="n">
+        <v>256334</v>
       </c>
     </row>
     <row r="39">
@@ -2793,20 +2886,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EU27_2020_FOR</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6638884</v>
+        <v>9818</v>
       </c>
       <c r="D39" t="n">
-        <v>14115497</v>
+        <v>13543</v>
       </c>
       <c r="E39" t="n">
-        <v>16354099</v>
+        <v>36473</v>
       </c>
       <c r="F39" t="n">
-        <v>17264800</v>
+        <v>36171</v>
+      </c>
+      <c r="G39" t="n">
+        <v>38562</v>
       </c>
     </row>
     <row r="40">
@@ -2817,20 +2913,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>Intra-EU27 (from 2020)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>70157831</v>
+        <v>68357968</v>
       </c>
       <c r="D40" t="n">
-        <v>119325095</v>
+        <v>68258991</v>
       </c>
       <c r="E40" t="n">
-        <v>133831926</v>
+        <v>114177531</v>
       </c>
       <c r="F40" t="n">
-        <v>137854964</v>
+        <v>127558032</v>
+      </c>
+      <c r="G40" t="n">
+        <v>131159611</v>
       </c>
     </row>
     <row r="41">
@@ -2841,20 +2940,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EUR_OTH</t>
+          <t>Intra-EU28 (2013-2020)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>209951</v>
+        <v>68952013</v>
       </c>
       <c r="D41" t="n">
-        <v>449527</v>
+        <v>68595025</v>
       </c>
       <c r="E41" t="n">
-        <v>579354</v>
+        <v>115601689</v>
       </c>
       <c r="F41" t="n">
-        <v>674020</v>
+        <v>129504190</v>
+      </c>
+      <c r="G41" t="n">
+        <v>133279089</v>
       </c>
     </row>
     <row r="42">
@@ -2865,20 +2967,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>58682</v>
+        <v>48172</v>
       </c>
       <c r="D42" t="n">
-        <v>202214</v>
+        <v>48192</v>
       </c>
       <c r="E42" t="n">
-        <v>231309</v>
+        <v>167249</v>
       </c>
       <c r="F42" t="n">
-        <v>235040</v>
+        <v>195063</v>
+      </c>
+      <c r="G42" t="n">
+        <v>204762</v>
       </c>
     </row>
     <row r="43">
@@ -2889,20 +2994,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>621147</v>
+        <v>445850</v>
       </c>
       <c r="D43" t="n">
-        <v>1322409</v>
+        <v>445572</v>
       </c>
       <c r="E43" t="n">
-        <v>1524189</v>
+        <v>1120323</v>
       </c>
       <c r="F43" t="n">
-        <v>1590854</v>
+        <v>1349533</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1407305</v>
       </c>
     </row>
     <row r="44">
@@ -2913,20 +3021,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>52081</v>
+        <v>92110</v>
       </c>
       <c r="D44" t="n">
-        <v>98962</v>
+        <v>26464</v>
       </c>
       <c r="E44" t="n">
-        <v>131684</v>
+        <v>126239</v>
       </c>
       <c r="F44" t="n">
-        <v>147406</v>
+        <v>263825</v>
+      </c>
+      <c r="G44" t="n">
+        <v>319214</v>
       </c>
     </row>
     <row r="45">
@@ -2937,20 +3048,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>86566</v>
+        <v>25465</v>
       </c>
       <c r="D45" t="n">
-        <v>181664</v>
+        <v>30956</v>
       </c>
       <c r="E45" t="n">
-        <v>228553</v>
+        <v>62896</v>
       </c>
       <c r="F45" t="n">
-        <v>256334</v>
+        <v>74546</v>
+      </c>
+      <c r="G45" t="n">
+        <v>79579</v>
       </c>
     </row>
     <row r="46">
@@ -2961,20 +3075,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>48192</v>
+        <v>37395</v>
       </c>
       <c r="D46" t="n">
-        <v>167249</v>
+        <v>46883</v>
       </c>
       <c r="E46" t="n">
-        <v>195063</v>
+        <v>99758</v>
       </c>
       <c r="F46" t="n">
-        <v>204762</v>
+        <v>113715</v>
+      </c>
+      <c r="G46" t="n">
+        <v>127404</v>
       </c>
     </row>
     <row r="47">
@@ -2985,20 +3102,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>INT_EU27_2020</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>68258991</v>
+        <v>97844</v>
       </c>
       <c r="D47" t="n">
-        <v>114177531</v>
+        <v>116742</v>
       </c>
       <c r="E47" t="n">
-        <v>127558032</v>
+        <v>227300</v>
       </c>
       <c r="F47" t="n">
-        <v>131159611</v>
+        <v>258432</v>
+      </c>
+      <c r="G47" t="n">
+        <v>266080</v>
       </c>
     </row>
     <row r="48">
@@ -3009,20 +3129,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INT_EU28</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>68595025</v>
+        <v>8166</v>
       </c>
       <c r="D48" t="n">
-        <v>115601689</v>
+        <v>8425</v>
       </c>
       <c r="E48" t="n">
-        <v>129504190</v>
+        <v>18984</v>
       </c>
       <c r="F48" t="n">
-        <v>133279089</v>
+        <v>23774</v>
+      </c>
+      <c r="G48" t="n">
+        <v>27787</v>
       </c>
     </row>
     <row r="49">
@@ -3033,20 +3156,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>13543</v>
+        <v>1585077</v>
       </c>
       <c r="D49" t="n">
-        <v>36473</v>
+        <v>1521276</v>
       </c>
       <c r="E49" t="n">
-        <v>36171</v>
+        <v>3262011</v>
       </c>
       <c r="F49" t="n">
-        <v>38562</v>
+        <v>3628869</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3809499</v>
       </c>
     </row>
     <row r="50">
@@ -3057,20 +3183,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Northern America</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>445572</v>
+        <v>631062</v>
       </c>
       <c r="D50" t="n">
-        <v>1120323</v>
+        <v>733586</v>
       </c>
       <c r="E50" t="n">
-        <v>1349533</v>
+        <v>2411013</v>
       </c>
       <c r="F50" t="n">
-        <v>1407305</v>
+        <v>3007559</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3385378</v>
       </c>
     </row>
     <row r="51">
@@ -3081,20 +3210,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>26464</v>
+        <v>66450</v>
       </c>
       <c r="D51" t="n">
-        <v>126239</v>
+        <v>72548</v>
       </c>
       <c r="E51" t="n">
-        <v>263825</v>
+        <v>277810</v>
       </c>
       <c r="F51" t="n">
-        <v>319214</v>
+        <v>292475</v>
+      </c>
+      <c r="G51" t="n">
+        <v>297367</v>
       </c>
     </row>
     <row r="52">
@@ -3105,20 +3237,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>25310</v>
+        <v>49334</v>
       </c>
       <c r="D52" t="n">
-        <v>110254</v>
+        <v>21060</v>
       </c>
       <c r="E52" t="n">
-        <v>208646</v>
+        <v>189691</v>
       </c>
       <c r="F52" t="n">
-        <v>210038</v>
+        <v>341277</v>
+      </c>
+      <c r="G52" t="n">
+        <v>346838</v>
       </c>
     </row>
     <row r="53">
@@ -3129,20 +3264,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>Other African countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>46883</v>
+        <v>52715</v>
       </c>
       <c r="D53" t="n">
-        <v>99758</v>
+        <v>48888</v>
       </c>
       <c r="E53" t="n">
-        <v>113715</v>
+        <v>137254</v>
       </c>
       <c r="F53" t="n">
-        <v>127404</v>
+        <v>164179</v>
+      </c>
+      <c r="G53" t="n">
+        <v>182129</v>
       </c>
     </row>
     <row r="54">
@@ -3153,20 +3291,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Other Asian countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>116742</v>
+        <v>382767</v>
       </c>
       <c r="D54" t="n">
-        <v>227300</v>
+        <v>430511</v>
       </c>
       <c r="E54" t="n">
-        <v>258432</v>
+        <v>1267391</v>
       </c>
       <c r="F54" t="n">
-        <v>266080</v>
+        <v>1679369</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1763293</v>
       </c>
     </row>
     <row r="55">
@@ -3177,20 +3318,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>Other Central or South American countries</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>30956</v>
+        <v>66868</v>
       </c>
       <c r="D55" t="n">
-        <v>62896</v>
+        <v>68364</v>
       </c>
       <c r="E55" t="n">
-        <v>74546</v>
+        <v>275453</v>
       </c>
       <c r="F55" t="n">
-        <v>79579</v>
+        <v>346603</v>
+      </c>
+      <c r="G55" t="n">
+        <v>379229</v>
       </c>
     </row>
     <row r="56">
@@ -3201,20 +3345,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>Other European countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8425</v>
+        <v>178300</v>
       </c>
       <c r="D56" t="n">
-        <v>18984</v>
+        <v>209951</v>
       </c>
       <c r="E56" t="n">
-        <v>23774</v>
+        <v>449527</v>
       </c>
       <c r="F56" t="n">
-        <v>27787</v>
+        <v>579354</v>
+      </c>
+      <c r="G56" t="n">
+        <v>674020</v>
       </c>
     </row>
     <row r="57">
@@ -3225,20 +3372,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Other Northern American countries</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1521276</v>
+        <v>4442</v>
       </c>
       <c r="D57" t="n">
-        <v>3262011</v>
+        <v>4221</v>
       </c>
       <c r="E57" t="n">
-        <v>3628869</v>
+        <v>19743</v>
       </c>
       <c r="F57" t="n">
-        <v>3809499</v>
+        <v>28272</v>
+      </c>
+      <c r="G57" t="n">
+        <v>32043</v>
       </c>
     </row>
     <row r="58">
@@ -3249,20 +3399,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Other Oceanian countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>72548</v>
+        <v>8482</v>
       </c>
       <c r="D58" t="n">
-        <v>277810</v>
+        <v>4840</v>
       </c>
       <c r="E58" t="n">
-        <v>292475</v>
+        <v>28565</v>
       </c>
       <c r="F58" t="n">
-        <v>297367</v>
+        <v>51019</v>
+      </c>
+      <c r="G58" t="n">
+        <v>54810</v>
       </c>
     </row>
     <row r="59">
@@ -3273,20 +3426,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OCE</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>21060</v>
+        <v>506647</v>
       </c>
       <c r="D59" t="n">
-        <v>189691</v>
+        <v>520773</v>
       </c>
       <c r="E59" t="n">
-        <v>341277</v>
+        <v>915622</v>
       </c>
       <c r="F59" t="n">
-        <v>346838</v>
+        <v>1154363</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1241170</v>
       </c>
     </row>
     <row r="60">
@@ -3297,20 +3453,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OCE_OTH</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4840</v>
+        <v>60541</v>
       </c>
       <c r="D60" t="n">
-        <v>28565</v>
+        <v>61422</v>
       </c>
       <c r="E60" t="n">
-        <v>51019</v>
+        <v>147695</v>
       </c>
       <c r="F60" t="n">
-        <v>54810</v>
+        <v>177036</v>
+      </c>
+      <c r="G60" t="n">
+        <v>190091</v>
       </c>
     </row>
     <row r="61">
@@ -3321,20 +3480,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>520773</v>
+        <v>153050</v>
       </c>
       <c r="D61" t="n">
-        <v>915622</v>
+        <v>160182</v>
       </c>
       <c r="E61" t="n">
-        <v>1154363</v>
+        <v>261763</v>
       </c>
       <c r="F61" t="n">
-        <v>1241170</v>
+        <v>313656</v>
+      </c>
+      <c r="G61" t="n">
+        <v>358758</v>
       </c>
     </row>
     <row r="62">
@@ -3345,20 +3507,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>61422</v>
+        <v>186423</v>
       </c>
       <c r="D62" t="n">
-        <v>147695</v>
+        <v>68611</v>
       </c>
       <c r="E62" t="n">
-        <v>177036</v>
+        <v>115260</v>
       </c>
       <c r="F62" t="n">
-        <v>190091</v>
+        <v>106678</v>
+      </c>
+      <c r="G62" t="n">
+        <v>98049</v>
       </c>
     </row>
     <row r="63">
@@ -3369,20 +3534,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>160182</v>
+        <v>59140</v>
       </c>
       <c r="D63" t="n">
-        <v>261763</v>
+        <v>61103</v>
       </c>
       <c r="E63" t="n">
-        <v>313656</v>
+        <v>117179</v>
       </c>
       <c r="F63" t="n">
-        <v>358758</v>
+        <v>141738</v>
+      </c>
+      <c r="G63" t="n">
+        <v>158683</v>
       </c>
     </row>
     <row r="64">
@@ -3393,20 +3561,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>68611</v>
+        <v>42960</v>
       </c>
       <c r="D64" t="n">
-        <v>115260</v>
+        <v>46654</v>
       </c>
       <c r="E64" t="n">
-        <v>106678</v>
+        <v>91635</v>
       </c>
       <c r="F64" t="n">
-        <v>98049</v>
+        <v>111465</v>
+      </c>
+      <c r="G64" t="n">
+        <v>122574</v>
       </c>
     </row>
     <row r="65">
@@ -3417,20 +3588,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>215285</v>
+        <v>14204</v>
       </c>
       <c r="D65" t="n">
-        <v>622106</v>
+        <v>7566</v>
       </c>
       <c r="E65" t="n">
-        <v>683951</v>
+        <v>41331</v>
       </c>
       <c r="F65" t="n">
-        <v>703323</v>
+        <v>47618</v>
+      </c>
+      <c r="G65" t="n">
+        <v>46435</v>
       </c>
     </row>
     <row r="66">
@@ -3441,20 +3615,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>46654</v>
+        <v>55400</v>
       </c>
       <c r="D66" t="n">
-        <v>91635</v>
+        <v>25310</v>
       </c>
       <c r="E66" t="n">
-        <v>111465</v>
+        <v>110254</v>
       </c>
       <c r="F66" t="n">
-        <v>122574</v>
+        <v>208646</v>
+      </c>
+      <c r="G66" t="n">
+        <v>210038</v>
       </c>
     </row>
     <row r="67">
@@ -3465,20 +3642,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>61103</v>
+        <v>288281</v>
       </c>
       <c r="D67" t="n">
-        <v>117179</v>
+        <v>312331</v>
       </c>
       <c r="E67" t="n">
-        <v>141738</v>
+        <v>802411</v>
       </c>
       <c r="F67" t="n">
-        <v>158683</v>
+        <v>934579</v>
+      </c>
+      <c r="G67" t="n">
+        <v>989197</v>
       </c>
     </row>
     <row r="68">
@@ -3489,20 +3669,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>85338</v>
+        <v>178859</v>
       </c>
       <c r="D68" t="n">
-        <v>258463</v>
+        <v>215285</v>
       </c>
       <c r="E68" t="n">
-        <v>373595</v>
+        <v>622106</v>
       </c>
       <c r="F68" t="n">
-        <v>450987</v>
+        <v>683951</v>
+      </c>
+      <c r="G68" t="n">
+        <v>703323</v>
       </c>
     </row>
     <row r="69">
@@ -3513,20 +3696,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UA</t>
+          <t>Switzerland and Liechtenstein</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>75379</v>
+        <v>1185330</v>
       </c>
       <c r="D69" t="n">
-        <v>252819</v>
+        <v>1037436</v>
       </c>
       <c r="E69" t="n">
-        <v>229265</v>
+        <v>2333054</v>
       </c>
       <c r="F69" t="n">
-        <v>230915</v>
+        <v>2710198</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2785975</v>
       </c>
     </row>
     <row r="70">
@@ -3537,20 +3723,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>336034</v>
+        <v>100155</v>
       </c>
       <c r="D70" t="n">
-        <v>1424158</v>
+        <v>85338</v>
       </c>
       <c r="E70" t="n">
-        <v>1946158</v>
+        <v>258463</v>
       </c>
       <c r="F70" t="n">
-        <v>2119478</v>
+        <v>373595</v>
+      </c>
+      <c r="G70" t="n">
+        <v>450987</v>
       </c>
     </row>
     <row r="71">
@@ -3561,20 +3750,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>673752</v>
+        <v>75558</v>
       </c>
       <c r="D71" t="n">
-        <v>2202334</v>
+        <v>75379</v>
       </c>
       <c r="E71" t="n">
-        <v>2729197</v>
+        <v>252819</v>
       </c>
       <c r="F71" t="n">
-        <v>3077771</v>
+        <v>229265</v>
+      </c>
+      <c r="G71" t="n">
+        <v>230915</v>
       </c>
     </row>
     <row r="72">
@@ -3585,20 +3777,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WORLD</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>71772542</v>
+        <v>594045</v>
       </c>
       <c r="D72" t="n">
-        <v>124601264</v>
+        <v>336034</v>
       </c>
       <c r="E72" t="n">
-        <v>141225234</v>
+        <v>1424158</v>
       </c>
       <c r="F72" t="n">
-        <v>146236303</v>
+        <v>1946158</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2119478</v>
       </c>
     </row>
     <row r="73">
@@ -3609,20 +3804,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WRL_NAL</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>173542</v>
+        <v>568965</v>
       </c>
       <c r="D73" t="n">
-        <v>380014</v>
+        <v>673752</v>
       </c>
       <c r="E73" t="n">
-        <v>562536</v>
+        <v>2202334</v>
       </c>
       <c r="F73" t="n">
-        <v>707698</v>
+        <v>2729197</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3077771</v>
       </c>
     </row>
     <row r="74">
@@ -3633,20 +3831,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>World - not allocated</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7566</v>
+        <v>241748</v>
       </c>
       <c r="D74" t="n">
-        <v>41331</v>
+        <v>173542</v>
       </c>
       <c r="E74" t="n">
-        <v>47618</v>
+        <v>380014</v>
       </c>
       <c r="F74" t="n">
-        <v>46435</v>
+        <v>562536</v>
+      </c>
+      <c r="G74" t="n">
+        <v>707698</v>
       </c>
     </row>
     <row r="75">
@@ -3657,19 +3858,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AFR</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C75" t="n">
+        <v>262141</v>
+      </c>
+      <c r="D75" t="n">
         <v>324358</v>
       </c>
-      <c r="D75" t="n">
+      <c r="E75" t="n">
         <v>712778</v>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>810575</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>906976</v>
       </c>
     </row>
@@ -3681,20 +3885,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AFR_OTH</t>
+          <t>All countries of the world</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>307436</v>
+        <v>34589072</v>
       </c>
       <c r="D76" t="n">
-        <v>655087</v>
+        <v>60724070</v>
       </c>
       <c r="E76" t="n">
-        <v>748780</v>
+        <v>102882568</v>
       </c>
       <c r="F76" t="n">
-        <v>839874</v>
+        <v>111991774</v>
+      </c>
+      <c r="G76" t="n">
+        <v>116166159</v>
       </c>
     </row>
     <row r="77">
@@ -3705,19 +3912,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>America</t>
         </is>
       </c>
       <c r="C77" t="n">
+        <v>1194081</v>
+      </c>
+      <c r="D77" t="n">
         <v>2165080</v>
       </c>
-      <c r="D77" t="n">
+      <c r="E77" t="n">
         <v>6670754</v>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>8396847</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>9248341</v>
       </c>
     </row>
@@ -3729,20 +3939,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AME_C_S</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>974915</v>
+        <v>744415</v>
       </c>
       <c r="D78" t="n">
-        <v>2488480</v>
+        <v>457427</v>
       </c>
       <c r="E78" t="n">
-        <v>2899254</v>
+        <v>1536313</v>
       </c>
       <c r="F78" t="n">
-        <v>3008629</v>
+        <v>2873094</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3707211</v>
       </c>
     </row>
     <row r="79">
@@ -3753,20 +3966,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AME_C_S_OTH</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>821044</v>
+        <v>32387</v>
       </c>
       <c r="D79" t="n">
-        <v>1983782</v>
+        <v>28679</v>
       </c>
       <c r="E79" t="n">
-        <v>2278354</v>
+        <v>212061</v>
       </c>
       <c r="F79" t="n">
-        <v>2314562</v>
+        <v>413058</v>
+      </c>
+      <c r="G79" t="n">
+        <v>431839</v>
       </c>
     </row>
     <row r="80">
@@ -3777,20 +3993,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AME_N</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1190166</v>
+        <v>76792</v>
       </c>
       <c r="D80" t="n">
-        <v>4182274</v>
+        <v>193788</v>
       </c>
       <c r="E80" t="n">
-        <v>5497593</v>
+        <v>480992</v>
       </c>
       <c r="F80" t="n">
-        <v>6239712</v>
+        <v>550660</v>
+      </c>
+      <c r="G80" t="n">
+        <v>586582</v>
       </c>
     </row>
     <row r="81">
@@ -3801,20 +4020,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AME_N_OTH</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>243554</v>
+        <v>336608</v>
       </c>
       <c r="D81" t="n">
-        <v>654719</v>
+        <v>783529</v>
       </c>
       <c r="E81" t="n">
-        <v>881830</v>
+        <v>1383994</v>
       </c>
       <c r="F81" t="n">
-        <v>945893</v>
+        <v>1433063</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1538185</v>
       </c>
     </row>
     <row r="82">
@@ -3825,20 +4047,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ASI</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>457427</v>
+        <v>147624</v>
       </c>
       <c r="D82" t="n">
-        <v>1536313</v>
+        <v>153870</v>
       </c>
       <c r="E82" t="n">
-        <v>2873094</v>
+        <v>504698</v>
       </c>
       <c r="F82" t="n">
-        <v>3707211</v>
+        <v>620900</v>
+      </c>
+      <c r="G82" t="n">
+        <v>694067</v>
       </c>
     </row>
     <row r="83">
@@ -3849,20 +4074,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ASI_OTH</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>302780</v>
+        <v>41720</v>
       </c>
       <c r="D83" t="n">
-        <v>939589</v>
+        <v>57425</v>
       </c>
       <c r="E83" t="n">
-        <v>1256888</v>
+        <v>115618</v>
       </c>
       <c r="F83" t="n">
-        <v>1400737</v>
+        <v>152373</v>
+      </c>
+      <c r="G83" t="n">
+        <v>166094</v>
       </c>
     </row>
     <row r="84">
@@ -3873,20 +4101,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>193788</v>
+        <v>72933</v>
       </c>
       <c r="D84" t="n">
-        <v>480992</v>
+        <v>74767</v>
       </c>
       <c r="E84" t="n">
-        <v>550660</v>
+        <v>449769</v>
       </c>
       <c r="F84" t="n">
-        <v>586582</v>
+        <v>663207</v>
+      </c>
+      <c r="G84" t="n">
+        <v>770769</v>
       </c>
     </row>
     <row r="85">
@@ -3897,20 +4128,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Central and South America</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>28679</v>
+        <v>641896</v>
       </c>
       <c r="D85" t="n">
-        <v>212061</v>
+        <v>974915</v>
       </c>
       <c r="E85" t="n">
-        <v>413058</v>
+        <v>2488480</v>
       </c>
       <c r="F85" t="n">
-        <v>431839</v>
+        <v>2899254</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3008629</v>
       </c>
     </row>
     <row r="86">
@@ -3921,20 +4155,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>783529</v>
+        <v>239985</v>
       </c>
       <c r="D86" t="n">
-        <v>1383994</v>
+        <v>106102</v>
       </c>
       <c r="E86" t="n">
-        <v>1433063</v>
+        <v>305178</v>
       </c>
       <c r="F86" t="n">
-        <v>1538185</v>
+        <v>763646</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1252057</v>
       </c>
     </row>
     <row r="87">
@@ -3945,20 +4182,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>57425</v>
+        <v>16190</v>
       </c>
       <c r="D87" t="n">
-        <v>115618</v>
+        <v>24356</v>
       </c>
       <c r="E87" t="n">
-        <v>152373</v>
+        <v>61664</v>
       </c>
       <c r="F87" t="n">
-        <v>166094</v>
+        <v>109492</v>
+      </c>
+      <c r="G87" t="n">
+        <v>135534</v>
       </c>
     </row>
     <row r="88">
@@ -3969,20 +4209,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>153870</v>
+        <v>3804</v>
       </c>
       <c r="D88" t="n">
-        <v>504698</v>
+        <v>5923</v>
       </c>
       <c r="E88" t="n">
-        <v>620900</v>
+        <v>16921</v>
       </c>
       <c r="F88" t="n">
-        <v>694067</v>
+        <v>21772</v>
+      </c>
+      <c r="G88" t="n">
+        <v>24581</v>
       </c>
     </row>
     <row r="89">
@@ -3993,20 +4236,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>74767</v>
+        <v>49531</v>
       </c>
       <c r="D89" t="n">
-        <v>449769</v>
+        <v>160833</v>
       </c>
       <c r="E89" t="n">
-        <v>663207</v>
+        <v>323945</v>
       </c>
       <c r="F89" t="n">
-        <v>770769</v>
+        <v>380627</v>
+      </c>
+      <c r="G89" t="n">
+        <v>392960</v>
       </c>
     </row>
     <row r="90">
@@ -4017,20 +4263,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CH_LI</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>505284</v>
+        <v>127966</v>
       </c>
       <c r="D90" t="n">
-        <v>956238</v>
+        <v>321064</v>
       </c>
       <c r="E90" t="n">
-        <v>1059999</v>
+        <v>595537</v>
       </c>
       <c r="F90" t="n">
-        <v>1118518</v>
+        <v>608568</v>
+      </c>
+      <c r="G90" t="n">
+        <v>621968</v>
       </c>
     </row>
     <row r="91">
@@ -4041,20 +4290,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>Domestic country</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>106102</v>
+        <v>23694815</v>
       </c>
       <c r="D91" t="n">
-        <v>305178</v>
+        <v>40272683</v>
       </c>
       <c r="E91" t="n">
-        <v>763646</v>
+        <v>53314484</v>
       </c>
       <c r="F91" t="n">
-        <v>1252057</v>
+        <v>54708067</v>
+      </c>
+      <c r="G91" t="n">
+        <v>54319372</v>
       </c>
     </row>
     <row r="92">
@@ -4065,20 +4317,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>EU27 countries (from 2020) except reporting country</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5923</v>
+        <v>6116591</v>
       </c>
       <c r="D92" t="n">
-        <v>16921</v>
+        <v>13295811</v>
       </c>
       <c r="E92" t="n">
-        <v>21772</v>
+        <v>27025008</v>
       </c>
       <c r="F92" t="n">
-        <v>24581</v>
+        <v>29908024</v>
+      </c>
+      <c r="G92" t="n">
+        <v>31815930</v>
       </c>
     </row>
     <row r="93">
@@ -4089,20 +4344,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>160833</v>
+        <v>14576</v>
       </c>
       <c r="D93" t="n">
-        <v>323945</v>
+        <v>32664</v>
       </c>
       <c r="E93" t="n">
-        <v>380627</v>
+        <v>72433</v>
       </c>
       <c r="F93" t="n">
-        <v>392960</v>
+        <v>80120</v>
+      </c>
+      <c r="G93" t="n">
+        <v>79302</v>
       </c>
     </row>
     <row r="94">
@@ -4113,20 +4371,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3085009</v>
+        <v>32145443</v>
       </c>
       <c r="D94" t="n">
-        <v>6592065</v>
+        <v>57350475</v>
       </c>
       <c r="E94" t="n">
-        <v>7238912</v>
+        <v>92903580</v>
       </c>
       <c r="F94" t="n">
-        <v>7656443</v>
+        <v>98560812</v>
+      </c>
+      <c r="G94" t="n">
+        <v>101070352</v>
       </c>
     </row>
     <row r="95">
@@ -4137,20 +4398,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>European Free Trade Association</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>321064</v>
+        <v>292430</v>
       </c>
       <c r="D95" t="n">
-        <v>595537</v>
+        <v>673017</v>
       </c>
       <c r="E95" t="n">
-        <v>608568</v>
+        <v>1634034</v>
       </c>
       <c r="F95" t="n">
-        <v>621968</v>
+        <v>1755162</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1813580</v>
       </c>
     </row>
     <row r="96">
@@ -4161,20 +4425,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>40272683</v>
+        <v>101513</v>
       </c>
       <c r="D96" t="n">
-        <v>53314484</v>
+        <v>107587</v>
       </c>
       <c r="E96" t="n">
-        <v>54708067</v>
+        <v>310612</v>
       </c>
       <c r="F96" t="n">
-        <v>54319372</v>
+        <v>358541</v>
+      </c>
+      <c r="G96" t="n">
+        <v>377572</v>
       </c>
     </row>
     <row r="97">
@@ -4185,20 +4452,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>32664</v>
+        <v>1664214</v>
       </c>
       <c r="D97" t="n">
-        <v>72433</v>
+        <v>3418911</v>
       </c>
       <c r="E97" t="n">
-        <v>80120</v>
+        <v>6030915</v>
       </c>
       <c r="F97" t="n">
-        <v>79302</v>
+        <v>6320145</v>
+      </c>
+      <c r="G97" t="n">
+        <v>6551945</v>
       </c>
     </row>
     <row r="98">
@@ -4209,20 +4479,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EFTA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>673017</v>
+        <v>1251116</v>
       </c>
       <c r="D98" t="n">
-        <v>1634034</v>
+        <v>3085009</v>
       </c>
       <c r="E98" t="n">
-        <v>1755162</v>
+        <v>6592065</v>
       </c>
       <c r="F98" t="n">
-        <v>1813580</v>
+        <v>7238912</v>
+      </c>
+      <c r="G98" t="n">
+        <v>7656443</v>
       </c>
     </row>
     <row r="99">
@@ -4233,19 +4506,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C99" t="n">
+        <v>28377</v>
+      </c>
+      <c r="D99" t="n">
         <v>53260</v>
       </c>
-      <c r="D99" t="n">
+      <c r="E99" t="n">
         <v>134287</v>
       </c>
-      <c r="E99" t="n">
+      <c r="F99" t="n">
         <v>162377</v>
       </c>
-      <c r="F99" t="n">
+      <c r="G99" t="n">
         <v>173550</v>
       </c>
     </row>
@@ -4257,20 +4533,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>40272683</v>
+        <v>35555</v>
       </c>
       <c r="D100" t="n">
-        <v>53314484</v>
+        <v>74359</v>
       </c>
       <c r="E100" t="n">
-        <v>54708067</v>
+        <v>178069</v>
       </c>
       <c r="F100" t="n">
-        <v>54319372</v>
+        <v>223884</v>
+      </c>
+      <c r="G100" t="n">
+        <v>262021</v>
       </c>
     </row>
     <row r="101">
@@ -4281,20 +4560,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EU27_2020_FOR</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>13295811</v>
+        <v>19399</v>
       </c>
       <c r="D101" t="n">
-        <v>27025008</v>
+        <v>42692</v>
       </c>
       <c r="E101" t="n">
-        <v>29908024</v>
+        <v>116241</v>
       </c>
       <c r="F101" t="n">
-        <v>31815930</v>
+        <v>123731</v>
+      </c>
+      <c r="G101" t="n">
+        <v>120000</v>
       </c>
     </row>
     <row r="102">
@@ -4305,20 +4587,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>Intra-EU27 (from 2020)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>57350475</v>
+        <v>29811406</v>
       </c>
       <c r="D102" t="n">
-        <v>92903580</v>
+        <v>53568494</v>
       </c>
       <c r="E102" t="n">
-        <v>98560812</v>
+        <v>80339492</v>
       </c>
       <c r="F102" t="n">
-        <v>101070352</v>
+        <v>84616091</v>
+      </c>
+      <c r="G102" t="n">
+        <v>86135302</v>
       </c>
     </row>
     <row r="103">
@@ -4329,20 +4614,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EUR_OTH</t>
+          <t>Intra-EU28 (2013-2020)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>338384</v>
+        <v>31408843</v>
       </c>
       <c r="D103" t="n">
-        <v>691163</v>
+        <v>56053493</v>
       </c>
       <c r="E103" t="n">
-        <v>707794</v>
+        <v>89929915</v>
       </c>
       <c r="F103" t="n">
-        <v>797419</v>
+        <v>95276457</v>
+      </c>
+      <c r="G103" t="n">
+        <v>97463076</v>
       </c>
     </row>
     <row r="104">
@@ -4353,20 +4641,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>107587</v>
+        <v>156240</v>
       </c>
       <c r="D104" t="n">
-        <v>310612</v>
+        <v>338504</v>
       </c>
       <c r="E104" t="n">
-        <v>358541</v>
+        <v>1149963</v>
       </c>
       <c r="F104" t="n">
-        <v>377572</v>
+        <v>1373471</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1535360</v>
       </c>
     </row>
     <row r="105">
@@ -4377,20 +4668,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3418911</v>
+        <v>606293</v>
       </c>
       <c r="D105" t="n">
-        <v>6030915</v>
+        <v>1160943</v>
       </c>
       <c r="E105" t="n">
-        <v>6320145</v>
+        <v>2771474</v>
       </c>
       <c r="F105" t="n">
-        <v>6551945</v>
+        <v>3245126</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3465211</v>
       </c>
     </row>
     <row r="106">
@@ -4401,20 +4695,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>24356</v>
+        <v>126256</v>
       </c>
       <c r="D106" t="n">
-        <v>61664</v>
+        <v>28472</v>
       </c>
       <c r="E106" t="n">
-        <v>109492</v>
+        <v>117539</v>
       </c>
       <c r="F106" t="n">
-        <v>135534</v>
+        <v>302873</v>
+      </c>
+      <c r="G106" t="n">
+        <v>399189</v>
       </c>
     </row>
     <row r="107">
@@ -4425,20 +4722,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>74359</v>
+        <v>13765</v>
       </c>
       <c r="D107" t="n">
-        <v>178069</v>
+        <v>31572</v>
       </c>
       <c r="E107" t="n">
-        <v>223884</v>
+        <v>74681</v>
       </c>
       <c r="F107" t="n">
-        <v>262021</v>
+        <v>80992</v>
+      </c>
+      <c r="G107" t="n">
+        <v>84675</v>
       </c>
     </row>
     <row r="108">
@@ -4449,20 +4749,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>338504</v>
+        <v>24806</v>
       </c>
       <c r="D108" t="n">
-        <v>1149963</v>
+        <v>59830</v>
       </c>
       <c r="E108" t="n">
-        <v>1373471</v>
+        <v>124767</v>
       </c>
       <c r="F108" t="n">
-        <v>1535360</v>
+        <v>152270</v>
+      </c>
+      <c r="G108" t="n">
+        <v>158731</v>
       </c>
     </row>
     <row r="109">
@@ -4473,20 +4776,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>INT_EU27_2020</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>53568494</v>
+        <v>26431</v>
       </c>
       <c r="D109" t="n">
-        <v>80339492</v>
+        <v>68829</v>
       </c>
       <c r="E109" t="n">
-        <v>84616091</v>
+        <v>92980</v>
       </c>
       <c r="F109" t="n">
-        <v>86135302</v>
+        <v>100197</v>
+      </c>
+      <c r="G109" t="n">
+        <v>103887</v>
       </c>
     </row>
     <row r="110">
@@ -4497,20 +4803,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>INT_EU28</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>56053493</v>
+        <v>5435</v>
       </c>
       <c r="D110" t="n">
-        <v>89929915</v>
+        <v>12038</v>
       </c>
       <c r="E110" t="n">
-        <v>95276457</v>
+        <v>31694</v>
       </c>
       <c r="F110" t="n">
-        <v>97463076</v>
+        <v>35689</v>
+      </c>
+      <c r="G110" t="n">
+        <v>39168</v>
       </c>
     </row>
     <row r="111">
@@ -4521,20 +4830,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>42692</v>
+        <v>457189</v>
       </c>
       <c r="D111" t="n">
-        <v>116241</v>
+        <v>1207273</v>
       </c>
       <c r="E111" t="n">
-        <v>123731</v>
+        <v>2317849</v>
       </c>
       <c r="F111" t="n">
-        <v>120000</v>
+        <v>2413034</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2595182</v>
       </c>
     </row>
     <row r="112">
@@ -4545,20 +4857,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Northern America</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1160943</v>
+        <v>552185</v>
       </c>
       <c r="D112" t="n">
-        <v>2771474</v>
+        <v>1190166</v>
       </c>
       <c r="E112" t="n">
-        <v>3245126</v>
+        <v>4182274</v>
       </c>
       <c r="F112" t="n">
-        <v>3465211</v>
+        <v>5497593</v>
+      </c>
+      <c r="G112" t="n">
+        <v>6239712</v>
       </c>
     </row>
     <row r="113">
@@ -4569,20 +4884,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>28472</v>
+        <v>160828</v>
       </c>
       <c r="D113" t="n">
-        <v>117539</v>
+        <v>125041</v>
       </c>
       <c r="E113" t="n">
-        <v>302873</v>
+        <v>561554</v>
       </c>
       <c r="F113" t="n">
-        <v>399189</v>
+        <v>571432</v>
+      </c>
+      <c r="G113" t="n">
+        <v>575061</v>
       </c>
     </row>
     <row r="114">
@@ -4593,20 +4911,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>20073</v>
+        <v>41658</v>
       </c>
       <c r="D114" t="n">
-        <v>174006</v>
+        <v>46202</v>
       </c>
       <c r="E114" t="n">
-        <v>549687</v>
+        <v>249351</v>
       </c>
       <c r="F114" t="n">
-        <v>655228</v>
+        <v>454323</v>
+      </c>
+      <c r="G114" t="n">
+        <v>467119</v>
       </c>
     </row>
     <row r="115">
@@ -4617,20 +4938,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>Other African countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>59830</v>
+        <v>250543</v>
       </c>
       <c r="D115" t="n">
-        <v>124767</v>
+        <v>307436</v>
       </c>
       <c r="E115" t="n">
-        <v>152270</v>
+        <v>655087</v>
       </c>
       <c r="F115" t="n">
-        <v>158731</v>
+        <v>748780</v>
+      </c>
+      <c r="G115" t="n">
+        <v>839874</v>
       </c>
     </row>
     <row r="116">
@@ -4641,20 +4965,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Other Asian countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>68829</v>
+        <v>212044</v>
       </c>
       <c r="D116" t="n">
-        <v>92980</v>
+        <v>302780</v>
       </c>
       <c r="E116" t="n">
-        <v>100197</v>
+        <v>939589</v>
       </c>
       <c r="F116" t="n">
-        <v>103887</v>
+        <v>1256888</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1400737</v>
       </c>
     </row>
     <row r="117">
@@ -4665,20 +4992,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>Other Central or South American countries</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>31572</v>
+        <v>494272</v>
       </c>
       <c r="D117" t="n">
-        <v>74681</v>
+        <v>821044</v>
       </c>
       <c r="E117" t="n">
-        <v>80992</v>
+        <v>1983782</v>
       </c>
       <c r="F117" t="n">
-        <v>84675</v>
+        <v>2278354</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2314562</v>
       </c>
     </row>
     <row r="118">
@@ -4689,20 +5019,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>Other European countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>12038</v>
+        <v>207464</v>
       </c>
       <c r="D118" t="n">
-        <v>31694</v>
+        <v>338384</v>
       </c>
       <c r="E118" t="n">
-        <v>35689</v>
+        <v>691163</v>
       </c>
       <c r="F118" t="n">
-        <v>39168</v>
+        <v>707794</v>
+      </c>
+      <c r="G118" t="n">
+        <v>797419</v>
       </c>
     </row>
     <row r="119">
@@ -4713,20 +5046,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Other Northern American countries</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1207273</v>
+        <v>97091</v>
       </c>
       <c r="D119" t="n">
-        <v>2317849</v>
+        <v>243554</v>
       </c>
       <c r="E119" t="n">
-        <v>2413034</v>
+        <v>654719</v>
       </c>
       <c r="F119" t="n">
-        <v>2595182</v>
+        <v>881830</v>
+      </c>
+      <c r="G119" t="n">
+        <v>945893</v>
       </c>
     </row>
     <row r="120">
@@ -4737,20 +5073,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Other Oceanian countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>125041</v>
+        <v>9271</v>
       </c>
       <c r="D120" t="n">
-        <v>561554</v>
+        <v>17523</v>
       </c>
       <c r="E120" t="n">
-        <v>571432</v>
+        <v>37290</v>
       </c>
       <c r="F120" t="n">
-        <v>575061</v>
+        <v>41265</v>
+      </c>
+      <c r="G120" t="n">
+        <v>35280</v>
       </c>
     </row>
     <row r="121">
@@ -4761,20 +5100,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>OCE</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>46202</v>
+        <v>212498</v>
       </c>
       <c r="D121" t="n">
-        <v>249351</v>
+        <v>472568</v>
       </c>
       <c r="E121" t="n">
-        <v>454323</v>
+        <v>924753</v>
       </c>
       <c r="F121" t="n">
-        <v>467119</v>
+        <v>1180598</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1388241</v>
       </c>
     </row>
     <row r="122">
@@ -4785,20 +5127,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>OCE_OTH</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>17523</v>
+        <v>409541</v>
       </c>
       <c r="D122" t="n">
-        <v>37290</v>
+        <v>849210</v>
       </c>
       <c r="E122" t="n">
-        <v>41265</v>
+        <v>1745126</v>
       </c>
       <c r="F122" t="n">
-        <v>35280</v>
+        <v>2030105</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2152251</v>
       </c>
     </row>
     <row r="123">
@@ -4809,20 +5154,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>472568</v>
+        <v>203707</v>
       </c>
       <c r="D123" t="n">
-        <v>924753</v>
+        <v>329501</v>
       </c>
       <c r="E123" t="n">
-        <v>1180598</v>
+        <v>551065</v>
       </c>
       <c r="F123" t="n">
-        <v>1388241</v>
+        <v>603075</v>
+      </c>
+      <c r="G123" t="n">
+        <v>639957</v>
       </c>
     </row>
     <row r="124">
@@ -4833,20 +5181,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>849210</v>
+        <v>144289</v>
       </c>
       <c r="D124" t="n">
-        <v>1745126</v>
+        <v>132069</v>
       </c>
       <c r="E124" t="n">
-        <v>2030105</v>
+        <v>228249</v>
       </c>
       <c r="F124" t="n">
-        <v>2152251</v>
+        <v>267705</v>
+      </c>
+      <c r="G124" t="n">
+        <v>277336</v>
       </c>
     </row>
     <row r="125">
@@ -4857,20 +5208,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>329501</v>
+        <v>14662</v>
       </c>
       <c r="D125" t="n">
-        <v>551065</v>
+        <v>46798</v>
       </c>
       <c r="E125" t="n">
-        <v>603075</v>
+        <v>110877</v>
       </c>
       <c r="F125" t="n">
-        <v>639957</v>
+        <v>127035</v>
+      </c>
+      <c r="G125" t="n">
+        <v>143767</v>
       </c>
     </row>
     <row r="126">
@@ -4881,20 +5235,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>132069</v>
+        <v>11048</v>
       </c>
       <c r="D126" t="n">
-        <v>228249</v>
+        <v>23050</v>
       </c>
       <c r="E126" t="n">
-        <v>267705</v>
+        <v>58836</v>
       </c>
       <c r="F126" t="n">
-        <v>277336</v>
+        <v>75999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>78437</v>
       </c>
     </row>
     <row r="127">
@@ -4905,20 +5262,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>376987</v>
+        <v>11598</v>
       </c>
       <c r="D127" t="n">
-        <v>773891</v>
+        <v>16921</v>
       </c>
       <c r="E127" t="n">
-        <v>849899</v>
+        <v>57691</v>
       </c>
       <c r="F127" t="n">
-        <v>864326</v>
+        <v>61795</v>
+      </c>
+      <c r="G127" t="n">
+        <v>67102</v>
       </c>
     </row>
     <row r="128">
@@ -4929,20 +5289,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>23050</v>
+        <v>166131</v>
       </c>
       <c r="D128" t="n">
-        <v>58836</v>
+        <v>20073</v>
       </c>
       <c r="E128" t="n">
-        <v>75999</v>
+        <v>174006</v>
       </c>
       <c r="F128" t="n">
-        <v>78437</v>
+        <v>549687</v>
+      </c>
+      <c r="G128" t="n">
+        <v>655228</v>
       </c>
     </row>
     <row r="129">
@@ -4953,20 +5316,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>46798</v>
+        <v>23694815</v>
       </c>
       <c r="D129" t="n">
-        <v>110877</v>
+        <v>40272683</v>
       </c>
       <c r="E129" t="n">
-        <v>127035</v>
+        <v>53314484</v>
       </c>
       <c r="F129" t="n">
-        <v>143767</v>
+        <v>54708067</v>
+      </c>
+      <c r="G129" t="n">
+        <v>54319372</v>
       </c>
     </row>
     <row r="130">
@@ -4977,20 +5343,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>41694</v>
+        <v>227014</v>
       </c>
       <c r="D130" t="n">
-        <v>152539</v>
+        <v>376987</v>
       </c>
       <c r="E130" t="n">
-        <v>231331</v>
+        <v>773891</v>
       </c>
       <c r="F130" t="n">
-        <v>301285</v>
+        <v>849899</v>
+      </c>
+      <c r="G130" t="n">
+        <v>864326</v>
       </c>
     </row>
     <row r="131">
@@ -5001,20 +5370,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>UA</t>
+          <t>Switzerland and Liechtenstein</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>111820</v>
+        <v>112203</v>
       </c>
       <c r="D131" t="n">
-        <v>267679</v>
+        <v>505284</v>
       </c>
       <c r="E131" t="n">
-        <v>322363</v>
+        <v>956238</v>
       </c>
       <c r="F131" t="n">
-        <v>417655</v>
+        <v>1059999</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1118518</v>
       </c>
     </row>
     <row r="132">
@@ -5025,20 +5397,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2484999</v>
+        <v>38836</v>
       </c>
       <c r="D132" t="n">
-        <v>9590423</v>
+        <v>41694</v>
       </c>
       <c r="E132" t="n">
-        <v>10660366</v>
+        <v>152539</v>
       </c>
       <c r="F132" t="n">
-        <v>11327774</v>
+        <v>231331</v>
+      </c>
+      <c r="G132" t="n">
+        <v>301285</v>
       </c>
     </row>
     <row r="133">
@@ -5049,20 +5424,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>871844</v>
+        <v>53579</v>
       </c>
       <c r="D133" t="n">
-        <v>3077786</v>
+        <v>111820</v>
       </c>
       <c r="E133" t="n">
-        <v>3952556</v>
+        <v>267679</v>
       </c>
       <c r="F133" t="n">
-        <v>4523050</v>
+        <v>322363</v>
+      </c>
+      <c r="G133" t="n">
+        <v>417655</v>
       </c>
     </row>
     <row r="134">
@@ -5073,20 +5451,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>WORLD</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>60724070</v>
+        <v>1597437</v>
       </c>
       <c r="D134" t="n">
-        <v>102882568</v>
+        <v>2484999</v>
       </c>
       <c r="E134" t="n">
-        <v>111991774</v>
+        <v>9590423</v>
       </c>
       <c r="F134" t="n">
-        <v>116166159</v>
+        <v>10660366</v>
+      </c>
+      <c r="G134" t="n">
+        <v>11327774</v>
       </c>
     </row>
     <row r="135">
@@ -5097,20 +5478,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>WRL_NAL</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>380528</v>
+        <v>382161</v>
       </c>
       <c r="D135" t="n">
-        <v>809792</v>
+        <v>871844</v>
       </c>
       <c r="E135" t="n">
-        <v>896124</v>
+        <v>3077786</v>
       </c>
       <c r="F135" t="n">
-        <v>766160</v>
+        <v>3952556</v>
+      </c>
+      <c r="G135" t="n">
+        <v>4523050</v>
       </c>
     </row>
     <row r="136">
@@ -5121,20 +5505,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>World - not allocated</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>16921</v>
+        <v>201333</v>
       </c>
       <c r="D136" t="n">
-        <v>57691</v>
+        <v>380528</v>
       </c>
       <c r="E136" t="n">
-        <v>61795</v>
+        <v>809792</v>
       </c>
       <c r="F136" t="n">
-        <v>67102</v>
+        <v>896124</v>
+      </c>
+      <c r="G136" t="n">
+        <v>766160</v>
       </c>
     </row>
     <row r="137">
@@ -5145,19 +5532,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>AFR</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C137" t="n">
+        <v>185032</v>
+      </c>
+      <c r="D137" t="n">
         <v>240290</v>
       </c>
-      <c r="D137" t="n">
+      <c r="E137" t="n">
         <v>574183</v>
       </c>
-      <c r="E137" t="n">
+      <c r="F137" t="n">
         <v>637151</v>
       </c>
-      <c r="F137" t="n">
+      <c r="G137" t="n">
         <v>644727</v>
       </c>
     </row>
@@ -5169,20 +5559,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AFR_OTH</t>
+          <t>All countries of the world</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>220248</v>
+        <v>59668239</v>
       </c>
       <c r="D138" t="n">
-        <v>527756</v>
+        <v>77227709</v>
       </c>
       <c r="E138" t="n">
-        <v>559543</v>
+        <v>115313668</v>
       </c>
       <c r="F138" t="n">
-        <v>592336</v>
+        <v>120732180</v>
+      </c>
+      <c r="G138" t="n">
+        <v>120181637</v>
       </c>
     </row>
     <row r="139">
@@ -5193,19 +5586,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>America</t>
         </is>
       </c>
       <c r="C139" t="n">
+        <v>949176</v>
+      </c>
+      <c r="D139" t="n">
         <v>1599126</v>
       </c>
-      <c r="D139" t="n">
+      <c r="E139" t="n">
         <v>4923450</v>
       </c>
-      <c r="E139" t="n">
+      <c r="F139" t="n">
         <v>5245644</v>
       </c>
-      <c r="F139" t="n">
+      <c r="G139" t="n">
         <v>6134823</v>
       </c>
     </row>
@@ -5217,20 +5613,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>AME_C_S</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>275538</v>
+        <v>725276</v>
       </c>
       <c r="D140" t="n">
-        <v>967995</v>
+        <v>749498</v>
       </c>
       <c r="E140" t="n">
-        <v>1147659</v>
+        <v>2023427</v>
       </c>
       <c r="F140" t="n">
-        <v>1198191</v>
+        <v>3071915</v>
+      </c>
+      <c r="G140" t="n">
+        <v>3168183</v>
       </c>
     </row>
     <row r="141">
@@ -5241,20 +5640,23 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>AME_C_S_OTH</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>176111</v>
+        <v>47488</v>
       </c>
       <c r="D141" t="n">
-        <v>592720</v>
+        <v>37338</v>
       </c>
       <c r="E141" t="n">
-        <v>692517</v>
+        <v>265992</v>
       </c>
       <c r="F141" t="n">
-        <v>726046</v>
+        <v>568360</v>
+      </c>
+      <c r="G141" t="n">
+        <v>471259</v>
       </c>
     </row>
     <row r="142">
@@ -5265,20 +5667,23 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>AME_N</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1323588</v>
+        <v>59308</v>
       </c>
       <c r="D142" t="n">
-        <v>3955456</v>
+        <v>122512</v>
       </c>
       <c r="E142" t="n">
-        <v>4097985</v>
+        <v>266828</v>
       </c>
       <c r="F142" t="n">
-        <v>4936633</v>
+        <v>287456</v>
+      </c>
+      <c r="G142" t="n">
+        <v>296202</v>
       </c>
     </row>
     <row r="143">
@@ -5289,20 +5694,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>AME_N_OTH</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>1401872</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>1946142</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>3209676</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>3137969</v>
+      </c>
+      <c r="G143" t="n">
+        <v>3212282</v>
       </c>
     </row>
     <row r="144">
@@ -5313,20 +5721,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ASI</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>749498</v>
+        <v>76787</v>
       </c>
       <c r="D144" t="n">
-        <v>2023427</v>
+        <v>99427</v>
       </c>
       <c r="E144" t="n">
-        <v>3071915</v>
+        <v>375275</v>
       </c>
       <c r="F144" t="n">
-        <v>3168183</v>
+        <v>455142</v>
+      </c>
+      <c r="G144" t="n">
+        <v>472145</v>
       </c>
     </row>
     <row r="145">
@@ -5337,20 +5748,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ASI_OTH</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>507834</v>
+        <v>19313</v>
       </c>
       <c r="D145" t="n">
-        <v>1516498</v>
+        <v>24863</v>
       </c>
       <c r="E145" t="n">
-        <v>1882258</v>
+        <v>57781</v>
       </c>
       <c r="F145" t="n">
-        <v>1758577</v>
+        <v>74899</v>
+      </c>
+      <c r="G145" t="n">
+        <v>71249</v>
       </c>
     </row>
     <row r="146">
@@ -5361,20 +5775,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>122512</v>
+        <v>77938</v>
       </c>
       <c r="D146" t="n">
-        <v>266828</v>
+        <v>109941</v>
       </c>
       <c r="E146" t="n">
-        <v>287456</v>
+        <v>434816</v>
       </c>
       <c r="F146" t="n">
-        <v>296202</v>
+        <v>558477</v>
+      </c>
+      <c r="G146" t="n">
+        <v>569791</v>
       </c>
     </row>
     <row r="147">
@@ -5385,20 +5802,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Central and South America</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>37338</v>
+        <v>177681</v>
       </c>
       <c r="D147" t="n">
-        <v>265992</v>
+        <v>275538</v>
       </c>
       <c r="E147" t="n">
-        <v>568360</v>
+        <v>967995</v>
       </c>
       <c r="F147" t="n">
-        <v>471259</v>
+        <v>1147659</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1198191</v>
       </c>
     </row>
     <row r="148">
@@ -5409,20 +5829,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1946142</v>
+        <v>270520</v>
       </c>
       <c r="D148" t="n">
-        <v>3209676</v>
+        <v>146058</v>
       </c>
       <c r="E148" t="n">
-        <v>3137969</v>
+        <v>224073</v>
       </c>
       <c r="F148" t="n">
-        <v>3212282</v>
+        <v>534737</v>
+      </c>
+      <c r="G148" t="n">
+        <v>732932</v>
       </c>
     </row>
     <row r="149">
@@ -5433,20 +5856,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>24863</v>
+        <v>8075</v>
       </c>
       <c r="D149" t="n">
-        <v>57781</v>
+        <v>13987</v>
       </c>
       <c r="E149" t="n">
-        <v>74899</v>
+        <v>37697</v>
       </c>
       <c r="F149" t="n">
-        <v>71249</v>
+        <v>58203</v>
+      </c>
+      <c r="G149" t="n">
+        <v>62387</v>
       </c>
     </row>
     <row r="150">
@@ -5457,20 +5883,23 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>99427</v>
+        <v>3606</v>
       </c>
       <c r="D150" t="n">
-        <v>375275</v>
+        <v>9478</v>
       </c>
       <c r="E150" t="n">
-        <v>455142</v>
+        <v>29037</v>
       </c>
       <c r="F150" t="n">
-        <v>472145</v>
+        <v>35172</v>
+      </c>
+      <c r="G150" t="n">
+        <v>33389</v>
       </c>
     </row>
     <row r="151">
@@ -5481,20 +5910,23 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>109941</v>
+        <v>40247</v>
       </c>
       <c r="D151" t="n">
-        <v>434816</v>
+        <v>63949</v>
       </c>
       <c r="E151" t="n">
-        <v>558477</v>
+        <v>149363</v>
       </c>
       <c r="F151" t="n">
-        <v>569791</v>
+        <v>182471</v>
+      </c>
+      <c r="G151" t="n">
+        <v>178589</v>
       </c>
     </row>
     <row r="152">
@@ -5505,20 +5937,23 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CH_LI</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1001607</v>
+        <v>62078</v>
       </c>
       <c r="D152" t="n">
-        <v>1940134</v>
+        <v>143514</v>
       </c>
       <c r="E152" t="n">
-        <v>1891196</v>
+        <v>310818</v>
       </c>
       <c r="F152" t="n">
-        <v>2050827</v>
+        <v>298869</v>
+      </c>
+      <c r="G152" t="n">
+        <v>290146</v>
       </c>
     </row>
     <row r="153">
@@ -5529,20 +5964,23 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>Domestic country</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>146058</v>
+        <v>49686164</v>
       </c>
       <c r="D153" t="n">
-        <v>224073</v>
+        <v>63472748</v>
       </c>
       <c r="E153" t="n">
-        <v>534737</v>
+        <v>82428128</v>
       </c>
       <c r="F153" t="n">
-        <v>732932</v>
+        <v>83304920</v>
+      </c>
+      <c r="G153" t="n">
+        <v>82336568</v>
       </c>
     </row>
     <row r="154">
@@ -5553,20 +5991,23 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>EU27 countries (from 2020) except reporting country</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>9478</v>
+        <v>5622215</v>
       </c>
       <c r="D154" t="n">
-        <v>29037</v>
+        <v>8429316</v>
       </c>
       <c r="E154" t="n">
-        <v>35172</v>
+        <v>17605161</v>
       </c>
       <c r="F154" t="n">
-        <v>33389</v>
+        <v>18367977</v>
+      </c>
+      <c r="G154" t="n">
+        <v>18524472</v>
       </c>
     </row>
     <row r="155">
@@ -5577,20 +6018,23 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>63949</v>
+        <v>7122</v>
       </c>
       <c r="D155" t="n">
-        <v>149363</v>
+        <v>15309</v>
       </c>
       <c r="E155" t="n">
-        <v>182471</v>
+        <v>37785</v>
       </c>
       <c r="F155" t="n">
-        <v>178589</v>
+        <v>35845</v>
+      </c>
+      <c r="G155" t="n">
+        <v>37419</v>
       </c>
     </row>
     <row r="156">
@@ -5601,20 +6045,23 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1780293</v>
+        <v>57761267</v>
       </c>
       <c r="D156" t="n">
-        <v>3607958</v>
+        <v>74601457</v>
       </c>
       <c r="E156" t="n">
-        <v>3844568</v>
+        <v>107526614</v>
       </c>
       <c r="F156" t="n">
-        <v>3875086</v>
+        <v>111209110</v>
+      </c>
+      <c r="G156" t="n">
+        <v>109762644</v>
       </c>
     </row>
     <row r="157">
@@ -5625,20 +6072,23 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>European Free Trade Association</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>143514</v>
+        <v>778208</v>
       </c>
       <c r="D157" t="n">
-        <v>310818</v>
+        <v>1061955</v>
       </c>
       <c r="E157" t="n">
-        <v>298869</v>
+        <v>2164157</v>
       </c>
       <c r="F157" t="n">
-        <v>290146</v>
+        <v>2149399</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2327560</v>
       </c>
     </row>
     <row r="158">
@@ -5649,20 +6099,23 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>63472748</v>
+        <v>25839</v>
       </c>
       <c r="D158" t="n">
-        <v>82428128</v>
+        <v>37902</v>
       </c>
       <c r="E158" t="n">
-        <v>83304920</v>
+        <v>114206</v>
       </c>
       <c r="F158" t="n">
-        <v>82336568</v>
+        <v>121729</v>
+      </c>
+      <c r="G158" t="n">
+        <v>120851</v>
       </c>
     </row>
     <row r="159">
@@ -5673,20 +6126,23 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>15309</v>
+        <v>49686164</v>
       </c>
       <c r="D159" t="n">
-        <v>37785</v>
+        <v>63472748</v>
       </c>
       <c r="E159" t="n">
-        <v>35845</v>
+        <v>82428128</v>
       </c>
       <c r="F159" t="n">
-        <v>37419</v>
+        <v>83304920</v>
+      </c>
+      <c r="G159" t="n">
+        <v>82336568</v>
       </c>
     </row>
     <row r="160">
@@ -5697,20 +6153,23 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EFTA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1061955</v>
+        <v>1163543</v>
       </c>
       <c r="D160" t="n">
-        <v>2164157</v>
+        <v>1780293</v>
       </c>
       <c r="E160" t="n">
-        <v>2149399</v>
+        <v>3607958</v>
       </c>
       <c r="F160" t="n">
-        <v>2327560</v>
+        <v>3844568</v>
+      </c>
+      <c r="G160" t="n">
+        <v>3875086</v>
       </c>
     </row>
     <row r="161">
@@ -5721,19 +6180,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C161" t="n">
+        <v>28118</v>
+      </c>
+      <c r="D161" t="n">
         <v>50970</v>
       </c>
-      <c r="D161" t="n">
+      <c r="E161" t="n">
         <v>139650</v>
       </c>
-      <c r="E161" t="n">
+      <c r="F161" t="n">
         <v>146901</v>
       </c>
-      <c r="F161" t="n">
+      <c r="G161" t="n">
         <v>153968</v>
       </c>
     </row>
@@ -5745,20 +6207,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>984927</v>
+        <v>19046</v>
       </c>
       <c r="D162" t="n">
-        <v>2459181</v>
+        <v>30557</v>
       </c>
       <c r="E162" t="n">
-        <v>2623571</v>
+        <v>76506</v>
       </c>
       <c r="F162" t="n">
-        <v>2629840</v>
+        <v>84295</v>
+      </c>
+      <c r="G162" t="n">
+        <v>85903</v>
       </c>
     </row>
     <row r="163">
@@ -5769,20 +6234,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EU27_2020_FOR</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>8429316</v>
+        <v>4610</v>
       </c>
       <c r="D163" t="n">
-        <v>17605161</v>
+        <v>8799</v>
       </c>
       <c r="E163" t="n">
-        <v>18367977</v>
+        <v>22336</v>
       </c>
       <c r="F163" t="n">
-        <v>18524472</v>
+        <v>21333</v>
+      </c>
+      <c r="G163" t="n">
+        <v>20812</v>
       </c>
     </row>
     <row r="164">
@@ -5793,20 +6261,23 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>Intra-EU27 (from 2020)</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>74601457</v>
+        <v>55308379</v>
       </c>
       <c r="D164" t="n">
-        <v>107526614</v>
+        <v>71902064</v>
       </c>
       <c r="E164" t="n">
-        <v>111209110</v>
+        <v>100033289</v>
       </c>
       <c r="F164" t="n">
-        <v>109762644</v>
+        <v>101672897</v>
+      </c>
+      <c r="G164" t="n">
+        <v>100861040</v>
       </c>
     </row>
     <row r="165">
@@ -5817,20 +6288,23 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EUR_OTH</t>
+          <t>Intra-EU28 (2013-2020)</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>304125</v>
+        <v>56629718</v>
       </c>
       <c r="D165" t="n">
-        <v>721061</v>
+        <v>73100752</v>
       </c>
       <c r="E165" t="n">
-        <v>803388</v>
+        <v>104364591</v>
       </c>
       <c r="F165" t="n">
-        <v>861861</v>
+        <v>107854014</v>
+      </c>
+      <c r="G165" t="n">
+        <v>106085555</v>
       </c>
     </row>
     <row r="166">
@@ -5841,20 +6315,23 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>37902</v>
+        <v>54840</v>
       </c>
       <c r="D166" t="n">
-        <v>114206</v>
+        <v>100832</v>
       </c>
       <c r="E166" t="n">
-        <v>121729</v>
+        <v>343276</v>
       </c>
       <c r="F166" t="n">
-        <v>120851</v>
+        <v>428712</v>
+      </c>
+      <c r="G166" t="n">
+        <v>407447</v>
       </c>
     </row>
     <row r="167">
@@ -5865,20 +6342,23 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>63472748</v>
+        <v>652337</v>
       </c>
       <c r="D167" t="n">
-        <v>82428128</v>
+        <v>882027</v>
       </c>
       <c r="E167" t="n">
-        <v>83304920</v>
+        <v>2271206</v>
       </c>
       <c r="F167" t="n">
-        <v>82336568</v>
+        <v>2462250</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2425656</v>
       </c>
     </row>
     <row r="168">
@@ -5889,20 +6369,23 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>13987</v>
+        <v>128985</v>
       </c>
       <c r="D168" t="n">
-        <v>37697</v>
+        <v>63972</v>
       </c>
       <c r="E168" t="n">
-        <v>58203</v>
+        <v>119407</v>
       </c>
       <c r="F168" t="n">
-        <v>62387</v>
+        <v>339113</v>
+      </c>
+      <c r="G168" t="n">
+        <v>392903</v>
       </c>
     </row>
     <row r="169">
@@ -5913,20 +6396,23 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>30557</v>
+        <v>7762</v>
       </c>
       <c r="D169" t="n">
-        <v>76506</v>
+        <v>12483</v>
       </c>
       <c r="E169" t="n">
-        <v>84295</v>
+        <v>34237</v>
       </c>
       <c r="F169" t="n">
-        <v>85903</v>
+        <v>35234</v>
+      </c>
+      <c r="G169" t="n">
+        <v>37793</v>
       </c>
     </row>
     <row r="170">
@@ -5937,20 +6423,23 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>100832</v>
+        <v>23484</v>
       </c>
       <c r="D170" t="n">
-        <v>343276</v>
+        <v>30848</v>
       </c>
       <c r="E170" t="n">
-        <v>428712</v>
+        <v>64109</v>
       </c>
       <c r="F170" t="n">
-        <v>407447</v>
+        <v>71413</v>
+      </c>
+      <c r="G170" t="n">
+        <v>69981</v>
       </c>
     </row>
     <row r="171">
@@ -5961,20 +6450,23 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>INT_EU27_2020</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>71902064</v>
+        <v>133908</v>
       </c>
       <c r="D171" t="n">
-        <v>100033289</v>
+        <v>164310</v>
       </c>
       <c r="E171" t="n">
-        <v>101672897</v>
+        <v>279348</v>
       </c>
       <c r="F171" t="n">
-        <v>100861040</v>
+        <v>284723</v>
+      </c>
+      <c r="G171" t="n">
+        <v>297370</v>
       </c>
     </row>
     <row r="172">
@@ -5985,20 +6477,23 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>INT_EU28</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>73100752</v>
+        <v>5102</v>
       </c>
       <c r="D172" t="n">
-        <v>104364591</v>
+        <v>9861</v>
       </c>
       <c r="E172" t="n">
-        <v>107854014</v>
+        <v>29064</v>
       </c>
       <c r="F172" t="n">
-        <v>106085555</v>
+        <v>33212</v>
+      </c>
+      <c r="G172" t="n">
+        <v>35119</v>
       </c>
     </row>
     <row r="173">
@@ -6009,20 +6504,23 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>8799</v>
+        <v>816398</v>
       </c>
       <c r="D173" t="n">
-        <v>22336</v>
+        <v>1317108</v>
       </c>
       <c r="E173" t="n">
-        <v>21333</v>
+        <v>2535866</v>
       </c>
       <c r="F173" t="n">
-        <v>20812</v>
+        <v>2393736</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2495789</v>
       </c>
     </row>
     <row r="174">
@@ -6033,20 +6531,23 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Northern America</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>882027</v>
+        <v>771495</v>
       </c>
       <c r="D174" t="n">
-        <v>2271206</v>
+        <v>1323588</v>
       </c>
       <c r="E174" t="n">
-        <v>2462250</v>
+        <v>3955456</v>
       </c>
       <c r="F174" t="n">
-        <v>2425656</v>
+        <v>4097985</v>
+      </c>
+      <c r="G174" t="n">
+        <v>4936633</v>
       </c>
     </row>
     <row r="175">
@@ -6057,20 +6558,23 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>63972</v>
+        <v>29016</v>
       </c>
       <c r="D175" t="n">
-        <v>119407</v>
+        <v>51550</v>
       </c>
       <c r="E175" t="n">
-        <v>339113</v>
+        <v>201687</v>
       </c>
       <c r="F175" t="n">
-        <v>392903</v>
+        <v>236869</v>
+      </c>
+      <c r="G175" t="n">
+        <v>255921</v>
       </c>
     </row>
     <row r="176">
@@ -6081,20 +6585,23 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>31633</v>
+        <v>47488</v>
       </c>
       <c r="D176" t="n">
-        <v>163450</v>
+        <v>37338</v>
       </c>
       <c r="E176" t="n">
-        <v>315807</v>
+        <v>265992</v>
       </c>
       <c r="F176" t="n">
-        <v>283771</v>
+        <v>568360</v>
+      </c>
+      <c r="G176" t="n">
+        <v>471259</v>
       </c>
     </row>
     <row r="177">
@@ -6105,20 +6612,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>Other African countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>30848</v>
+        <v>165988</v>
       </c>
       <c r="D177" t="n">
-        <v>64109</v>
+        <v>220248</v>
       </c>
       <c r="E177" t="n">
-        <v>71413</v>
+        <v>527756</v>
       </c>
       <c r="F177" t="n">
-        <v>69981</v>
+        <v>559543</v>
+      </c>
+      <c r="G177" t="n">
+        <v>592336</v>
       </c>
     </row>
     <row r="178">
@@ -6129,20 +6639,23 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Other Asian countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>164310</v>
+        <v>275548</v>
       </c>
       <c r="D178" t="n">
-        <v>279348</v>
+        <v>507834</v>
       </c>
       <c r="E178" t="n">
-        <v>284723</v>
+        <v>1516498</v>
       </c>
       <c r="F178" t="n">
-        <v>297370</v>
+        <v>1882258</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1758577</v>
       </c>
     </row>
     <row r="179">
@@ -6153,20 +6666,23 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>Other Central or South American countries</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>12483</v>
+        <v>100894</v>
       </c>
       <c r="D179" t="n">
-        <v>34237</v>
+        <v>176111</v>
       </c>
       <c r="E179" t="n">
-        <v>35234</v>
+        <v>592720</v>
       </c>
       <c r="F179" t="n">
-        <v>37793</v>
+        <v>692517</v>
+      </c>
+      <c r="G179" t="n">
+        <v>726046</v>
       </c>
     </row>
     <row r="180">
@@ -6177,20 +6693,23 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>Other European countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>9861</v>
+        <v>198301</v>
       </c>
       <c r="D180" t="n">
-        <v>29064</v>
+        <v>304125</v>
       </c>
       <c r="E180" t="n">
-        <v>33212</v>
+        <v>721061</v>
       </c>
       <c r="F180" t="n">
-        <v>35119</v>
+        <v>803388</v>
+      </c>
+      <c r="G180" t="n">
+        <v>861861</v>
       </c>
     </row>
     <row r="181">
@@ -6201,20 +6720,23 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Other Northern American countries</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1317108</v>
+        <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>2535866</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>2393736</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>2495789</v>
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -6225,20 +6747,23 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Other Oceanian countries (aggregate changing according to the context)</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>51550</v>
+        <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>201687</v>
+        <v>0</v>
       </c>
       <c r="E182" t="n">
-        <v>236869</v>
+        <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>255921</v>
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -6249,20 +6774,23 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>OCE</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>37338</v>
+        <v>118942</v>
       </c>
       <c r="D183" t="n">
-        <v>265992</v>
+        <v>242003</v>
       </c>
       <c r="E183" t="n">
-        <v>568360</v>
+        <v>487329</v>
       </c>
       <c r="F183" t="n">
-        <v>471259</v>
+        <v>558150</v>
+      </c>
+      <c r="G183" t="n">
+        <v>544664</v>
       </c>
     </row>
     <row r="184">
@@ -6273,20 +6801,23 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>OCE_OTH</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>135816</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>181248</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>453881</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>490790</v>
+      </c>
+      <c r="G184" t="n">
+        <v>481259</v>
       </c>
     </row>
     <row r="185">
@@ -6297,20 +6828,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>242003</v>
+        <v>88512</v>
       </c>
       <c r="D185" t="n">
-        <v>487329</v>
+        <v>115948</v>
       </c>
       <c r="E185" t="n">
-        <v>558150</v>
+        <v>232195</v>
       </c>
       <c r="F185" t="n">
-        <v>544664</v>
+        <v>249225</v>
+      </c>
+      <c r="G185" t="n">
+        <v>243859</v>
       </c>
     </row>
     <row r="186">
@@ -6321,20 +6855,23 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>181248</v>
+        <v>112529</v>
       </c>
       <c r="D186" t="n">
-        <v>453881</v>
+        <v>85984</v>
       </c>
       <c r="E186" t="n">
-        <v>490790</v>
+        <v>122840</v>
       </c>
       <c r="F186" t="n">
-        <v>481259</v>
+        <v>163377</v>
+      </c>
+      <c r="G186" t="n">
+        <v>181684</v>
       </c>
     </row>
     <row r="187">
@@ -6345,20 +6882,23 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>115948</v>
+        <v>10245</v>
       </c>
       <c r="D187" t="n">
-        <v>232195</v>
+        <v>15590</v>
       </c>
       <c r="E187" t="n">
-        <v>249225</v>
+        <v>41916</v>
       </c>
       <c r="F187" t="n">
-        <v>243859</v>
+        <v>52857</v>
+      </c>
+      <c r="G187" t="n">
+        <v>55473</v>
       </c>
     </row>
     <row r="188">
@@ -6369,20 +6909,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>85984</v>
+        <v>7492</v>
       </c>
       <c r="D188" t="n">
-        <v>122840</v>
+        <v>14614</v>
       </c>
       <c r="E188" t="n">
-        <v>163377</v>
+        <v>33998</v>
       </c>
       <c r="F188" t="n">
-        <v>181684</v>
+        <v>38193</v>
+      </c>
+      <c r="G188" t="n">
+        <v>37657</v>
       </c>
     </row>
     <row r="189">
@@ -6393,20 +6936,23 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>118041</v>
+        <v>19044</v>
       </c>
       <c r="D189" t="n">
-        <v>302250</v>
+        <v>20042</v>
       </c>
       <c r="E189" t="n">
-        <v>337534</v>
+        <v>46427</v>
       </c>
       <c r="F189" t="n">
-        <v>345094</v>
+        <v>77608</v>
+      </c>
+      <c r="G189" t="n">
+        <v>52391</v>
       </c>
     </row>
     <row r="190">
@@ -6417,20 +6963,23 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>14614</v>
+        <v>50222</v>
       </c>
       <c r="D190" t="n">
-        <v>33998</v>
+        <v>31633</v>
       </c>
       <c r="E190" t="n">
-        <v>38193</v>
+        <v>163450</v>
       </c>
       <c r="F190" t="n">
-        <v>37657</v>
+        <v>315807</v>
+      </c>
+      <c r="G190" t="n">
+        <v>283771</v>
       </c>
     </row>
     <row r="191">
@@ -6441,20 +6990,23 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>15590</v>
+        <v>663005</v>
       </c>
       <c r="D191" t="n">
-        <v>41916</v>
+        <v>984927</v>
       </c>
       <c r="E191" t="n">
-        <v>52857</v>
+        <v>2459181</v>
       </c>
       <c r="F191" t="n">
-        <v>55473</v>
+        <v>2623571</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2629840</v>
       </c>
     </row>
     <row r="192">
@@ -6465,20 +7017,23 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>48642</v>
+        <v>66205</v>
       </c>
       <c r="D192" t="n">
-        <v>153964</v>
+        <v>118041</v>
       </c>
       <c r="E192" t="n">
-        <v>238931</v>
+        <v>302250</v>
       </c>
       <c r="F192" t="n">
-        <v>305987</v>
+        <v>337534</v>
+      </c>
+      <c r="G192" t="n">
+        <v>345094</v>
       </c>
     </row>
     <row r="193">
@@ -6489,20 +7044,23 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>UA</t>
+          <t>Switzerland and Liechtenstein</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0</v>
+        <v>744583</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>1001607</v>
       </c>
       <c r="E193" t="n">
-        <v>0</v>
+        <v>1940134</v>
       </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>1891196</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2050827</v>
       </c>
     </row>
     <row r="194">
@@ -6513,20 +7071,23 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1198688</v>
+        <v>42510</v>
       </c>
       <c r="D194" t="n">
-        <v>4331302</v>
+        <v>48642</v>
       </c>
       <c r="E194" t="n">
-        <v>6181117</v>
+        <v>153964</v>
       </c>
       <c r="F194" t="n">
-        <v>5224515</v>
+        <v>238931</v>
+      </c>
+      <c r="G194" t="n">
+        <v>305987</v>
       </c>
     </row>
     <row r="195">
@@ -6537,20 +7098,23 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1213647</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>3520640</v>
+        <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>3539509</v>
+        <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>4366842</v>
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -6561,20 +7125,23 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>WORLD</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>77227709</v>
+        <v>1321339</v>
       </c>
       <c r="D196" t="n">
-        <v>115313668</v>
+        <v>1198688</v>
       </c>
       <c r="E196" t="n">
-        <v>120732180</v>
+        <v>4331302</v>
       </c>
       <c r="F196" t="n">
-        <v>120181637</v>
+        <v>6181117</v>
+      </c>
+      <c r="G196" t="n">
+        <v>5224515</v>
       </c>
     </row>
     <row r="197">
@@ -6585,20 +7152,23 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>WRL_NAL</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>693557</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>1213647</v>
       </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>3520640</v>
       </c>
       <c r="F197" t="n">
-        <v>0</v>
+        <v>3539509</v>
+      </c>
+      <c r="G197" t="n">
+        <v>4366842</v>
       </c>
     </row>
     <row r="198">
@@ -6609,20 +7179,23 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>World - not allocated</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>20042</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>46427</v>
+        <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>77608</v>
+        <v>1</v>
       </c>
       <c r="F198" t="n">
-        <v>52391</v>
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -6639,15 +7212,18 @@
         </is>
       </c>
       <c r="B204" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C204" t="n">
         <v>2021</v>
       </c>
-      <c r="C204" t="n">
+      <c r="D204" t="n">
         <v>2022</v>
       </c>
-      <c r="D204" t="n">
+      <c r="E204" t="n">
         <v>2023</v>
       </c>
-      <c r="E204" t="n">
+      <c r="F204" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -6658,15 +7234,18 @@
         </is>
       </c>
       <c r="B205" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="C205" t="n">
         <v>481.68</v>
       </c>
-      <c r="C205" t="n">
+      <c r="D205" t="n">
         <v>690.59</v>
       </c>
-      <c r="D205" t="n">
+      <c r="E205" t="n">
         <v>705.28</v>
       </c>
-      <c r="E205" t="n">
+      <c r="F205" t="n">
         <v>729.0700000000001</v>
       </c>
     </row>
@@ -6677,15 +7256,18 @@
         </is>
       </c>
       <c r="B206" t="n">
+        <v>223.79</v>
+      </c>
+      <c r="C206" t="n">
         <v>241.51</v>
       </c>
-      <c r="C206" t="n">
+      <c r="D206" t="n">
         <v>314.18</v>
       </c>
-      <c r="D206" t="n">
+      <c r="E206" t="n">
         <v>346.72</v>
       </c>
-      <c r="E206" t="n">
+      <c r="F206" t="n">
         <v>367.6</v>
       </c>
     </row>
@@ -6696,15 +7278,18 @@
         </is>
       </c>
       <c r="B207" t="n">
+        <v>335.75</v>
+      </c>
+      <c r="C207" t="n">
         <v>324.99</v>
       </c>
-      <c r="C207" t="n">
+      <c r="D207" t="n">
         <v>394.36</v>
       </c>
-      <c r="D207" t="n">
+      <c r="E207" t="n">
         <v>406.75</v>
       </c>
-      <c r="E207" t="n">
+      <c r="F207" t="n">
         <v>424.77</v>
       </c>
     </row>
@@ -6727,30 +7312,33 @@
         </is>
       </c>
       <c r="C213" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D213" t="n">
         <v>2016</v>
       </c>
-      <c r="D213" t="n">
+      <c r="E213" t="n">
         <v>2017</v>
       </c>
-      <c r="E213" t="n">
+      <c r="F213" t="n">
         <v>2018</v>
       </c>
-      <c r="F213" t="n">
+      <c r="G213" t="n">
         <v>2019</v>
       </c>
-      <c r="G213" t="n">
+      <c r="H213" t="n">
         <v>2020</v>
       </c>
-      <c r="H213" t="n">
+      <c r="I213" t="n">
         <v>2021</v>
       </c>
-      <c r="I213" t="n">
+      <c r="J213" t="n">
         <v>2022</v>
       </c>
-      <c r="J213" t="n">
+      <c r="K213" t="n">
         <v>2023</v>
       </c>
-      <c r="K213" t="n">
+      <c r="L213" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -6766,30 +7354,33 @@
         </is>
       </c>
       <c r="C214" t="n">
+        <v>299220311</v>
+      </c>
+      <c r="D214" t="n">
         <v>308904957</v>
       </c>
-      <c r="D214" t="n">
+      <c r="E214" t="n">
         <v>318051999</v>
       </c>
-      <c r="E214" t="n">
+      <c r="F214" t="n">
         <v>332594428</v>
       </c>
-      <c r="F214" t="n">
+      <c r="G214" t="n">
         <v>347694001</v>
       </c>
-      <c r="G214" t="n">
+      <c r="H214" t="n">
         <v>229025364</v>
       </c>
-      <c r="H214" t="n">
+      <c r="I214" t="n">
         <v>235371154</v>
       </c>
-      <c r="I214" t="n">
+      <c r="J214" t="n">
         <v>332792753</v>
       </c>
-      <c r="J214" t="n">
+      <c r="K214" t="n">
         <v>351060606</v>
       </c>
-      <c r="K214" t="n">
+      <c r="L214" t="n">
         <v>354827032</v>
       </c>
     </row>
@@ -6805,30 +7396,33 @@
         </is>
       </c>
       <c r="C215" t="n">
+        <v>78827773</v>
+      </c>
+      <c r="D215" t="n">
         <v>79946914</v>
       </c>
-      <c r="D215" t="n">
+      <c r="E215" t="n">
         <v>83111219</v>
       </c>
-      <c r="E215" t="n">
+      <c r="F215" t="n">
         <v>86961856</v>
       </c>
-      <c r="F215" t="n">
+      <c r="G215" t="n">
         <v>89260847</v>
       </c>
-      <c r="G215" t="n">
+      <c r="H215" t="n">
         <v>31732508</v>
       </c>
-      <c r="H215" t="n">
+      <c r="I215" t="n">
         <v>30731500</v>
       </c>
-      <c r="I215" t="n">
+      <c r="J215" t="n">
         <v>67616302</v>
       </c>
-      <c r="J215" t="n">
+      <c r="K215" t="n">
         <v>80378429</v>
       </c>
-      <c r="K215" t="n">
+      <c r="L215" t="n">
         <v>84792636</v>
       </c>
     </row>
@@ -6844,30 +7438,33 @@
         </is>
       </c>
       <c r="C216" t="n">
+        <v>378048084</v>
+      </c>
+      <c r="D216" t="n">
         <v>388851871</v>
       </c>
-      <c r="D216" t="n">
+      <c r="E216" t="n">
         <v>401163218</v>
       </c>
-      <c r="E216" t="n">
+      <c r="F216" t="n">
         <v>419556284</v>
       </c>
-      <c r="F216" t="n">
+      <c r="G216" t="n">
         <v>436954848</v>
       </c>
-      <c r="G216" t="n">
+      <c r="H216" t="n">
         <v>260757872</v>
       </c>
-      <c r="H216" t="n">
+      <c r="I216" t="n">
         <v>266102654</v>
       </c>
-      <c r="I216" t="n">
+      <c r="J216" t="n">
         <v>400409055</v>
       </c>
-      <c r="J216" t="n">
+      <c r="K216" t="n">
         <v>431439035</v>
       </c>
-      <c r="K216" t="n">
+      <c r="L216" t="n">
         <v>439619668</v>
       </c>
     </row>
@@ -6883,30 +7480,33 @@
         </is>
       </c>
       <c r="C217" t="n">
+        <v>152808273</v>
+      </c>
+      <c r="D217" t="n">
         <v>160400822</v>
       </c>
-      <c r="D217" t="n">
+      <c r="E217" t="n">
         <v>165292267</v>
       </c>
-      <c r="E217" t="n">
+      <c r="F217" t="n">
         <v>165918083</v>
       </c>
-      <c r="F217" t="n">
+      <c r="G217" t="n">
         <v>170722142</v>
       </c>
-      <c r="G217" t="n">
+      <c r="H217" t="n">
         <v>83778193</v>
       </c>
-      <c r="H217" t="n">
+      <c r="I217" t="n">
         <v>145188204</v>
       </c>
-      <c r="I217" t="n">
+      <c r="J217" t="n">
         <v>180184036</v>
       </c>
-      <c r="J217" t="n">
+      <c r="K217" t="n">
         <v>183129528</v>
       </c>
-      <c r="K217" t="n">
+      <c r="L217" t="n">
         <v>182936205</v>
       </c>
     </row>
@@ -6922,30 +7522,33 @@
         </is>
       </c>
       <c r="C218" t="n">
+        <v>269418103</v>
+      </c>
+      <c r="D218" t="n">
         <v>294556428</v>
       </c>
-      <c r="D218" t="n">
+      <c r="E218" t="n">
         <v>305907462</v>
       </c>
-      <c r="E218" t="n">
+      <c r="F218" t="n">
         <v>301022634</v>
       </c>
-      <c r="F218" t="n">
+      <c r="G218" t="n">
         <v>299091409</v>
       </c>
-      <c r="G218" t="n">
+      <c r="H218" t="n">
         <v>60898835</v>
       </c>
-      <c r="H218" t="n">
+      <c r="I218" t="n">
         <v>114391555</v>
       </c>
-      <c r="I218" t="n">
+      <c r="J218" t="n">
         <v>271440904</v>
       </c>
-      <c r="J218" t="n">
+      <c r="K218" t="n">
         <v>301857957</v>
       </c>
-      <c r="K218" t="n">
+      <c r="L218" t="n">
         <v>322229807</v>
       </c>
     </row>
@@ -6961,30 +7564,33 @@
         </is>
       </c>
       <c r="C219" t="n">
+        <v>422226376</v>
+      </c>
+      <c r="D219" t="n">
         <v>454957250</v>
       </c>
-      <c r="D219" t="n">
+      <c r="E219" t="n">
         <v>471199729</v>
       </c>
-      <c r="E219" t="n">
+      <c r="F219" t="n">
         <v>466940717</v>
       </c>
-      <c r="F219" t="n">
+      <c r="G219" t="n">
         <v>469813551</v>
       </c>
-      <c r="G219" t="n">
+      <c r="H219" t="n">
         <v>144677028</v>
       </c>
-      <c r="H219" t="n">
+      <c r="I219" t="n">
         <v>259579759</v>
       </c>
-      <c r="I219" t="n">
+      <c r="J219" t="n">
         <v>451624940</v>
       </c>
-      <c r="J219" t="n">
+      <c r="K219" t="n">
         <v>484987485</v>
       </c>
-      <c r="K219" t="n">
+      <c r="L219" t="n">
         <v>505166012</v>
       </c>
     </row>
@@ -7000,30 +7606,33 @@
         </is>
       </c>
       <c r="C220" t="n">
+        <v>279587890</v>
+      </c>
+      <c r="D220" t="n">
         <v>280850016</v>
       </c>
-      <c r="D220" t="n">
+      <c r="E220" t="n">
         <v>299558737</v>
       </c>
-      <c r="E220" t="n">
+      <c r="F220" t="n">
         <v>302038667</v>
       </c>
-      <c r="F220" t="n">
+      <c r="G220" t="n">
         <v>310563771</v>
       </c>
-      <c r="G220" t="n">
+      <c r="H220" t="n">
         <v>212781655</v>
       </c>
-      <c r="H220" t="n">
+      <c r="I220" t="n">
         <v>267865936</v>
       </c>
-      <c r="I220" t="n">
+      <c r="J220" t="n">
         <v>324342680</v>
       </c>
-      <c r="J220" t="n">
+      <c r="K220" t="n">
         <v>321903813</v>
       </c>
-      <c r="K220" t="n">
+      <c r="L220" t="n">
         <v>317036065</v>
       </c>
     </row>
@@ -7039,30 +7648,33 @@
         </is>
       </c>
       <c r="C221" t="n">
+        <v>130464997</v>
+      </c>
+      <c r="D221" t="n">
         <v>123913410</v>
       </c>
-      <c r="D221" t="n">
+      <c r="E221" t="n">
         <v>133499991</v>
       </c>
-      <c r="E221" t="n">
+      <c r="F221" t="n">
         <v>140721383</v>
       </c>
-      <c r="F221" t="n">
+      <c r="G221" t="n">
         <v>135990097</v>
       </c>
-      <c r="G221" t="n">
+      <c r="H221" t="n">
         <v>45093660</v>
       </c>
-      <c r="H221" t="n">
+      <c r="I221" t="n">
         <v>56523110</v>
       </c>
-      <c r="I221" t="n">
+      <c r="J221" t="n">
         <v>125449581</v>
       </c>
-      <c r="J221" t="n">
+      <c r="K221" t="n">
         <v>138367983</v>
       </c>
-      <c r="K221" t="n">
+      <c r="L221" t="n">
         <v>140608197</v>
       </c>
     </row>
@@ -7078,30 +7690,33 @@
         </is>
       </c>
       <c r="C222" t="n">
+        <v>410052887</v>
+      </c>
+      <c r="D222" t="n">
         <v>404763426</v>
       </c>
-      <c r="D222" t="n">
+      <c r="E222" t="n">
         <v>433058728</v>
       </c>
-      <c r="E222" t="n">
+      <c r="F222" t="n">
         <v>442760050</v>
       </c>
-      <c r="F222" t="n">
+      <c r="G222" t="n">
         <v>446553868</v>
       </c>
-      <c r="G222" t="n">
+      <c r="H222" t="n">
         <v>257875315</v>
       </c>
-      <c r="H222" t="n">
+      <c r="I222" t="n">
         <v>324389046</v>
       </c>
-      <c r="I222" t="n">
+      <c r="J222" t="n">
         <v>449792261</v>
       </c>
-      <c r="J222" t="n">
+      <c r="K222" t="n">
         <v>460271796</v>
       </c>
-      <c r="K222" t="n">
+      <c r="L222" t="n">
         <v>457644262</v>
       </c>
     </row>
@@ -7124,30 +7739,33 @@
         </is>
       </c>
       <c r="C228" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D228" t="n">
         <v>2016</v>
       </c>
-      <c r="D228" t="n">
+      <c r="E228" t="n">
         <v>2017</v>
       </c>
-      <c r="E228" t="n">
+      <c r="F228" t="n">
         <v>2018</v>
       </c>
-      <c r="F228" t="n">
+      <c r="G228" t="n">
         <v>2019</v>
       </c>
-      <c r="G228" t="n">
+      <c r="H228" t="n">
         <v>2020</v>
       </c>
-      <c r="H228" t="n">
+      <c r="I228" t="n">
         <v>2021</v>
       </c>
-      <c r="I228" t="n">
+      <c r="J228" t="n">
         <v>2022</v>
       </c>
-      <c r="J228" t="n">
+      <c r="K228" t="n">
         <v>2023</v>
       </c>
-      <c r="K228" t="n">
+      <c r="L228" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -7163,30 +7781,33 @@
         </is>
       </c>
       <c r="C229" t="n">
+        <v>1311808356</v>
+      </c>
+      <c r="D229" t="n">
         <v>1360097876</v>
       </c>
-      <c r="D229" t="n">
+      <c r="E229" t="n">
         <v>1349363024</v>
       </c>
-      <c r="E229" t="n">
+      <c r="F229" t="n">
         <v>1498547146</v>
       </c>
-      <c r="F229" t="n">
+      <c r="G229" t="n">
         <v>1453638850</v>
       </c>
-      <c r="G229" t="n">
+      <c r="H229" t="n">
         <v>777640211</v>
       </c>
-      <c r="H229" t="n">
+      <c r="I229" t="n">
         <v>956814825</v>
       </c>
-      <c r="I229" t="n">
+      <c r="J229" t="n">
         <v>1317453011</v>
       </c>
-      <c r="J229" t="n">
+      <c r="K229" t="n">
         <v>1413423364</v>
       </c>
-      <c r="K229" t="n">
+      <c r="L229" t="n">
         <v>1560613457</v>
       </c>
     </row>
@@ -7202,30 +7823,33 @@
         </is>
       </c>
       <c r="C230" t="n">
+        <v>1048387561</v>
+      </c>
+      <c r="D230" t="n">
         <v>1100275260</v>
       </c>
-      <c r="D230" t="n">
+      <c r="E230" t="n">
         <v>1100693273</v>
       </c>
-      <c r="E230" t="n">
+      <c r="F230" t="n">
         <v>1234343369</v>
       </c>
-      <c r="F230" t="n">
+      <c r="G230" t="n">
         <v>1187749886</v>
       </c>
-      <c r="G230" t="n">
+      <c r="H230" t="n">
         <v>625363795</v>
       </c>
-      <c r="H230" t="n">
+      <c r="I230" t="n">
         <v>774417132</v>
       </c>
-      <c r="I230" t="n">
+      <c r="J230" t="n">
         <v>1105829691</v>
       </c>
-      <c r="J230" t="n">
+      <c r="K230" t="n">
         <v>1170772096</v>
       </c>
-      <c r="K230" t="n">
+      <c r="L230" t="n">
         <v>1294962255</v>
       </c>
     </row>
@@ -7241,30 +7865,33 @@
         </is>
       </c>
       <c r="C231" t="n">
+        <v>263420794</v>
+      </c>
+      <c r="D231" t="n">
         <v>259822616</v>
       </c>
-      <c r="D231" t="n">
+      <c r="E231" t="n">
         <v>248669751</v>
       </c>
-      <c r="E231" t="n">
+      <c r="F231" t="n">
         <v>264203777</v>
       </c>
-      <c r="F231" t="n">
+      <c r="G231" t="n">
         <v>265888963</v>
       </c>
-      <c r="G231" t="n">
+      <c r="H231" t="n">
         <v>152276417</v>
       </c>
-      <c r="H231" t="n">
+      <c r="I231" t="n">
         <v>182397693</v>
       </c>
-      <c r="I231" t="n">
+      <c r="J231" t="n">
         <v>211623320</v>
       </c>
-      <c r="J231" t="n">
+      <c r="K231" t="n">
         <v>242651269</v>
       </c>
-      <c r="K231" t="n">
+      <c r="L231" t="n">
         <v>265651201</v>
       </c>
     </row>
@@ -7280,30 +7907,33 @@
         </is>
       </c>
       <c r="C232" t="n">
+        <v>583440923</v>
+      </c>
+      <c r="D232" t="n">
         <v>621877918</v>
       </c>
-      <c r="D232" t="n">
+      <c r="E232" t="n">
         <v>629592329</v>
       </c>
-      <c r="E232" t="n">
+      <c r="F232" t="n">
         <v>627151621</v>
       </c>
-      <c r="F232" t="n">
+      <c r="G232" t="n">
         <v>630274720</v>
       </c>
-      <c r="G232" t="n">
+      <c r="H232" t="n">
         <v>388322337</v>
       </c>
-      <c r="H232" t="n">
+      <c r="I232" t="n">
         <v>497409766</v>
       </c>
-      <c r="I232" t="n">
+      <c r="J232" t="n">
         <v>605192168</v>
       </c>
-      <c r="J232" t="n">
+      <c r="K232" t="n">
         <v>635376640</v>
       </c>
-      <c r="K232" t="n">
+      <c r="L232" t="n">
         <v>656113949</v>
       </c>
     </row>
@@ -7319,30 +7949,33 @@
         </is>
       </c>
       <c r="C233" t="n">
+        <v>406146658</v>
+      </c>
+      <c r="D233" t="n">
         <v>435322266</v>
       </c>
-      <c r="D233" t="n">
+      <c r="E233" t="n">
         <v>432931093</v>
       </c>
-      <c r="E233" t="n">
+      <c r="F233" t="n">
         <v>428852318</v>
       </c>
-      <c r="F233" t="n">
+      <c r="G233" t="n">
         <v>433463477</v>
       </c>
-      <c r="G233" t="n">
+      <c r="H233" t="n">
         <v>290483006</v>
       </c>
-      <c r="H233" t="n">
+      <c r="I233" t="n">
         <v>354537241</v>
       </c>
-      <c r="I233" t="n">
+      <c r="J233" t="n">
         <v>429848653</v>
       </c>
-      <c r="J233" t="n">
+      <c r="K233" t="n">
         <v>451064703</v>
       </c>
-      <c r="K233" t="n">
+      <c r="L233" t="n">
         <v>467754713</v>
       </c>
     </row>
@@ -7358,30 +7991,33 @@
         </is>
       </c>
       <c r="C234" t="n">
+        <v>177294265</v>
+      </c>
+      <c r="D234" t="n">
         <v>186555651</v>
       </c>
-      <c r="D234" t="n">
+      <c r="E234" t="n">
         <v>196661236</v>
       </c>
-      <c r="E234" t="n">
+      <c r="F234" t="n">
         <v>198299303</v>
       </c>
-      <c r="F234" t="n">
+      <c r="G234" t="n">
         <v>196811244</v>
       </c>
-      <c r="G234" t="n">
+      <c r="H234" t="n">
         <v>97839332</v>
       </c>
-      <c r="H234" t="n">
+      <c r="I234" t="n">
         <v>142872525</v>
       </c>
-      <c r="I234" t="n">
+      <c r="J234" t="n">
         <v>175343515</v>
       </c>
-      <c r="J234" t="n">
+      <c r="K234" t="n">
         <v>184311937</v>
       </c>
-      <c r="K234" t="n">
+      <c r="L234" t="n">
         <v>188359236</v>
       </c>
     </row>
@@ -7397,30 +8033,33 @@
         </is>
       </c>
       <c r="C235" t="n">
+        <v>1113942857</v>
+      </c>
+      <c r="D235" t="n">
         <v>1094125171</v>
       </c>
-      <c r="D235" t="n">
+      <c r="E235" t="n">
         <v>1127833720</v>
       </c>
-      <c r="E235" t="n">
+      <c r="F235" t="n">
         <v>1138617385</v>
       </c>
-      <c r="F235" t="n">
+      <c r="G235" t="n">
         <v>1092847613</v>
       </c>
-      <c r="G235" t="n">
+      <c r="H235" t="n">
         <v>849084834</v>
       </c>
-      <c r="H235" t="n">
+      <c r="I235" t="n">
         <v>960977930</v>
       </c>
-      <c r="I235" t="n">
+      <c r="J235" t="n">
         <v>1079731907</v>
       </c>
-      <c r="J235" t="n">
+      <c r="K235" t="n">
         <v>1123634836</v>
       </c>
-      <c r="K235" t="n">
+      <c r="L235" t="n">
         <v>1117657902</v>
       </c>
     </row>
@@ -7436,30 +8075,33 @@
         </is>
       </c>
       <c r="C236" t="n">
+        <v>920445926</v>
+      </c>
+      <c r="D236" t="n">
         <v>903876580</v>
       </c>
-      <c r="D236" t="n">
+      <c r="E236" t="n">
         <v>905716188</v>
       </c>
-      <c r="E236" t="n">
+      <c r="F236" t="n">
         <v>923194540</v>
       </c>
-      <c r="F236" t="n">
+      <c r="G236" t="n">
         <v>876928819</v>
       </c>
-      <c r="G236" t="n">
+      <c r="H236" t="n">
         <v>682714729</v>
       </c>
-      <c r="H236" t="n">
+      <c r="I236" t="n">
         <v>744355783</v>
       </c>
-      <c r="I236" t="n">
+      <c r="J236" t="n">
         <v>827429861</v>
       </c>
-      <c r="J236" t="n">
+      <c r="K236" t="n">
         <v>865880077</v>
       </c>
-      <c r="K236" t="n">
+      <c r="L236" t="n">
         <v>863472780</v>
       </c>
     </row>
@@ -7475,30 +8117,33 @@
         </is>
       </c>
       <c r="C237" t="n">
+        <v>193496931</v>
+      </c>
+      <c r="D237" t="n">
         <v>190248591</v>
       </c>
-      <c r="D237" t="n">
+      <c r="E237" t="n">
         <v>222117533</v>
       </c>
-      <c r="E237" t="n">
+      <c r="F237" t="n">
         <v>215422845</v>
       </c>
-      <c r="F237" t="n">
+      <c r="G237" t="n">
         <v>215918793</v>
       </c>
-      <c r="G237" t="n">
+      <c r="H237" t="n">
         <v>166370106</v>
       </c>
-      <c r="H237" t="n">
+      <c r="I237" t="n">
         <v>216622148</v>
       </c>
-      <c r="I237" t="n">
+      <c r="J237" t="n">
         <v>252302046</v>
       </c>
-      <c r="J237" t="n">
+      <c r="K237" t="n">
         <v>257754759</v>
       </c>
-      <c r="K237" t="n">
+      <c r="L237" t="n">
         <v>254185122</v>
       </c>
     </row>
@@ -7517,300 +8162,360 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
           <t>2021-01</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="O243" t="inlineStr">
         <is>
           <t>2021-02</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="P243" t="inlineStr">
         <is>
           <t>2021-03</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="Q243" t="inlineStr">
         <is>
           <t>2021-04</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
+      <c r="R243" t="inlineStr">
         <is>
           <t>2021-05</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
+      <c r="S243" t="inlineStr">
         <is>
           <t>2021-06</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
+      <c r="T243" t="inlineStr">
         <is>
           <t>2021-07</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
+      <c r="U243" t="inlineStr">
         <is>
           <t>2021-08</t>
         </is>
       </c>
-      <c r="J243" t="inlineStr">
+      <c r="V243" t="inlineStr">
         <is>
           <t>2021-09</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="W243" t="inlineStr">
         <is>
           <t>2021-10</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>2021-11</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr">
+      <c r="Y243" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
       </c>
-      <c r="N243" t="inlineStr">
+      <c r="Z243" t="inlineStr">
         <is>
           <t>2022-01</t>
         </is>
       </c>
-      <c r="O243" t="inlineStr">
+      <c r="AA243" t="inlineStr">
         <is>
           <t>2022-02</t>
         </is>
       </c>
-      <c r="P243" t="inlineStr">
+      <c r="AB243" t="inlineStr">
         <is>
           <t>2022-03</t>
         </is>
       </c>
-      <c r="Q243" t="inlineStr">
+      <c r="AC243" t="inlineStr">
         <is>
           <t>2022-04</t>
         </is>
       </c>
-      <c r="R243" t="inlineStr">
+      <c r="AD243" t="inlineStr">
         <is>
           <t>2022-05</t>
         </is>
       </c>
-      <c r="S243" t="inlineStr">
+      <c r="AE243" t="inlineStr">
         <is>
           <t>2022-06</t>
         </is>
       </c>
-      <c r="T243" t="inlineStr">
+      <c r="AF243" t="inlineStr">
         <is>
           <t>2022-07</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="AG243" t="inlineStr">
         <is>
           <t>2022-08</t>
         </is>
       </c>
-      <c r="V243" t="inlineStr">
+      <c r="AH243" t="inlineStr">
         <is>
           <t>2022-09</t>
         </is>
       </c>
-      <c r="W243" t="inlineStr">
+      <c r="AI243" t="inlineStr">
         <is>
           <t>2022-10</t>
         </is>
       </c>
-      <c r="X243" t="inlineStr">
+      <c r="AJ243" t="inlineStr">
         <is>
           <t>2022-11</t>
         </is>
       </c>
-      <c r="Y243" t="inlineStr">
+      <c r="AK243" t="inlineStr">
         <is>
           <t>2022-12</t>
         </is>
       </c>
-      <c r="Z243" t="inlineStr">
+      <c r="AL243" t="inlineStr">
         <is>
           <t>2023-01</t>
         </is>
       </c>
-      <c r="AA243" t="inlineStr">
+      <c r="AM243" t="inlineStr">
         <is>
           <t>2023-02</t>
         </is>
       </c>
-      <c r="AB243" t="inlineStr">
+      <c r="AN243" t="inlineStr">
         <is>
           <t>2023-03</t>
         </is>
       </c>
-      <c r="AC243" t="inlineStr">
+      <c r="AO243" t="inlineStr">
         <is>
           <t>2023-04</t>
         </is>
       </c>
-      <c r="AD243" t="inlineStr">
+      <c r="AP243" t="inlineStr">
         <is>
           <t>2023-05</t>
         </is>
       </c>
-      <c r="AE243" t="inlineStr">
+      <c r="AQ243" t="inlineStr">
         <is>
           <t>2023-06</t>
         </is>
       </c>
-      <c r="AF243" t="inlineStr">
+      <c r="AR243" t="inlineStr">
         <is>
           <t>2023-07</t>
         </is>
       </c>
-      <c r="AG243" t="inlineStr">
+      <c r="AS243" t="inlineStr">
         <is>
           <t>2023-08</t>
         </is>
       </c>
-      <c r="AH243" t="inlineStr">
+      <c r="AT243" t="inlineStr">
         <is>
           <t>2023-09</t>
         </is>
       </c>
-      <c r="AI243" t="inlineStr">
+      <c r="AU243" t="inlineStr">
         <is>
           <t>2023-10</t>
         </is>
       </c>
-      <c r="AJ243" t="inlineStr">
+      <c r="AV243" t="inlineStr">
         <is>
           <t>2023-11</t>
         </is>
       </c>
-      <c r="AK243" t="inlineStr">
+      <c r="AW243" t="inlineStr">
         <is>
           <t>2023-12</t>
         </is>
       </c>
-      <c r="AL243" t="inlineStr">
+      <c r="AX243" t="inlineStr">
         <is>
           <t>2024-01</t>
         </is>
       </c>
-      <c r="AM243" t="inlineStr">
+      <c r="AY243" t="inlineStr">
         <is>
           <t>2024-02</t>
         </is>
       </c>
-      <c r="AN243" t="inlineStr">
+      <c r="AZ243" t="inlineStr">
         <is>
           <t>2024-03</t>
         </is>
       </c>
-      <c r="AO243" t="inlineStr">
+      <c r="BA243" t="inlineStr">
         <is>
           <t>2024-04</t>
         </is>
       </c>
-      <c r="AP243" t="inlineStr">
+      <c r="BB243" t="inlineStr">
         <is>
           <t>2024-05</t>
         </is>
       </c>
-      <c r="AQ243" t="inlineStr">
+      <c r="BC243" t="inlineStr">
         <is>
           <t>2024-06</t>
         </is>
       </c>
-      <c r="AR243" t="inlineStr">
+      <c r="BD243" t="inlineStr">
         <is>
           <t>2024-07</t>
         </is>
       </c>
-      <c r="AS243" t="inlineStr">
+      <c r="BE243" t="inlineStr">
         <is>
           <t>2024-08</t>
         </is>
       </c>
-      <c r="AT243" t="inlineStr">
+      <c r="BF243" t="inlineStr">
         <is>
           <t>2024-09</t>
         </is>
       </c>
-      <c r="AU243" t="inlineStr">
+      <c r="BG243" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="AV243" t="inlineStr">
+      <c r="BH243" t="inlineStr">
         <is>
           <t>2024-11</t>
         </is>
       </c>
-      <c r="AW243" t="inlineStr">
+      <c r="BI243" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="AX243" t="inlineStr">
+      <c r="BJ243" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="AY243" t="inlineStr">
+      <c r="BK243" t="inlineStr">
         <is>
           <t>2025-02</t>
         </is>
       </c>
-      <c r="AZ243" t="inlineStr">
+      <c r="BL243" t="inlineStr">
         <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="BA243" t="inlineStr">
+      <c r="BM243" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="BB243" t="inlineStr">
+      <c r="BN243" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="BC243" t="inlineStr">
+      <c r="BO243" t="inlineStr">
         <is>
           <t>2025-06</t>
         </is>
       </c>
-      <c r="BD243" t="inlineStr">
+      <c r="BP243" t="inlineStr">
         <is>
           <t>2025-07</t>
         </is>
       </c>
-      <c r="BE243" t="inlineStr">
+      <c r="BQ243" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
       </c>
-      <c r="BF243" t="inlineStr">
+      <c r="BR243" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="BG243" t="inlineStr">
+      <c r="BS243" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="BH243" t="inlineStr">
+      <c r="BT243" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="BI243" t="inlineStr">
+      <c r="BU243" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
@@ -7823,183 +8528,219 @@
         </is>
       </c>
       <c r="B244" t="n">
+        <v>18300414</v>
+      </c>
+      <c r="C244" t="n">
+        <v>20030473</v>
+      </c>
+      <c r="D244" t="n">
+        <v>9331495</v>
+      </c>
+      <c r="E244" t="n">
+        <v>2313819</v>
+      </c>
+      <c r="F244" t="n">
+        <v>5078500</v>
+      </c>
+      <c r="G244" t="n">
+        <v>13767381</v>
+      </c>
+      <c r="H244" t="n">
+        <v>21735709</v>
+      </c>
+      <c r="I244" t="n">
+        <v>24341387</v>
+      </c>
+      <c r="J244" t="n">
+        <v>23117196</v>
+      </c>
+      <c r="K244" t="n">
+        <v>18193422</v>
+      </c>
+      <c r="L244" t="n">
+        <v>4776614</v>
+      </c>
+      <c r="M244" t="n">
+        <v>3343168</v>
+      </c>
+      <c r="N244" t="n">
         <v>3209294</v>
       </c>
-      <c r="C244" t="n">
+      <c r="O244" t="n">
         <v>3680276</v>
       </c>
-      <c r="D244" t="n">
+      <c r="P244" t="n">
         <v>4833748</v>
       </c>
-      <c r="E244" t="n">
+      <c r="Q244" t="n">
         <v>4313827</v>
       </c>
-      <c r="F244" t="n">
+      <c r="R244" t="n">
         <v>6296483</v>
       </c>
-      <c r="G244" t="n">
+      <c r="S244" t="n">
         <v>14544417</v>
       </c>
-      <c r="H244" t="n">
+      <c r="T244" t="n">
         <v>23735851</v>
       </c>
-      <c r="I244" t="n">
+      <c r="U244" t="n">
         <v>28680054</v>
       </c>
-      <c r="J244" t="n">
+      <c r="V244" t="n">
         <v>26071312</v>
       </c>
-      <c r="K244" t="n">
+      <c r="W244" t="n">
         <v>25775735</v>
       </c>
-      <c r="L244" t="n">
+      <c r="X244" t="n">
         <v>16000970</v>
       </c>
-      <c r="M244" t="n">
+      <c r="Y244" t="n">
         <v>11022029</v>
       </c>
-      <c r="N244" t="n">
+      <c r="Z244" t="n">
         <v>9753998</v>
       </c>
-      <c r="O244" t="n">
+      <c r="AA244" t="n">
         <v>11746293</v>
       </c>
-      <c r="P244" t="n">
+      <c r="AB244" t="n">
         <v>15968557</v>
       </c>
-      <c r="Q244" t="n">
+      <c r="AC244" t="n">
         <v>21151677</v>
       </c>
-      <c r="R244" t="n">
+      <c r="AD244" t="n">
         <v>25767015</v>
       </c>
-      <c r="S244" t="n">
+      <c r="AE244" t="n">
         <v>27651728</v>
       </c>
-      <c r="T244" t="n">
+      <c r="AF244" t="n">
         <v>30148806</v>
       </c>
-      <c r="U244" t="n">
+      <c r="AG244" t="n">
         <v>30705284</v>
       </c>
-      <c r="V244" t="n">
+      <c r="AH244" t="n">
         <v>28729296</v>
       </c>
-      <c r="W244" t="n">
+      <c r="AI244" t="n">
         <v>27345051</v>
       </c>
-      <c r="X244" t="n">
+      <c r="AJ244" t="n">
         <v>20322409</v>
       </c>
-      <c r="Y244" t="n">
+      <c r="AK244" t="n">
         <v>19248998</v>
       </c>
-      <c r="Z244" t="n">
+      <c r="AL244" t="n">
         <v>15721651</v>
       </c>
-      <c r="AA244" t="n">
+      <c r="AM244" t="n">
         <v>17527018</v>
       </c>
-      <c r="AB244" t="n">
+      <c r="AN244" t="n">
         <v>20930316</v>
       </c>
-      <c r="AC244" t="n">
+      <c r="AO244" t="n">
         <v>24264182</v>
       </c>
-      <c r="AD244" t="n">
+      <c r="AP244" t="n">
         <v>27481821</v>
       </c>
-      <c r="AE244" t="n">
+      <c r="AQ244" t="n">
         <v>28314877</v>
       </c>
-      <c r="AF244" t="n">
+      <c r="AR244" t="n">
         <v>30119477</v>
       </c>
-      <c r="AG244" t="n">
+      <c r="AS244" t="n">
         <v>30111892</v>
       </c>
-      <c r="AH244" t="n">
+      <c r="AT244" t="n">
         <v>29936523</v>
       </c>
-      <c r="AI244" t="n">
+      <c r="AU244" t="n">
         <v>27348012</v>
       </c>
-      <c r="AJ244" t="n">
+      <c r="AV244" t="n">
         <v>21192965</v>
       </c>
-      <c r="AK244" t="n">
+      <c r="AW244" t="n">
         <v>21047084</v>
       </c>
-      <c r="AL244" t="n">
+      <c r="AX244" t="n">
         <v>16575999</v>
       </c>
-      <c r="AM244" t="n">
+      <c r="AY244" t="n">
         <v>18587309</v>
       </c>
-      <c r="AN244" t="n">
+      <c r="AZ244" t="n">
         <v>22578534</v>
       </c>
-      <c r="AO244" t="n">
+      <c r="BA244" t="n">
         <v>23140339</v>
       </c>
-      <c r="AP244" t="n">
+      <c r="BB244" t="n">
         <v>27874429</v>
       </c>
-      <c r="AQ244" t="n">
+      <c r="BC244" t="n">
         <v>28591632</v>
       </c>
-      <c r="AR244" t="n">
+      <c r="BD244" t="n">
         <v>30434400</v>
       </c>
-      <c r="AS244" t="n">
+      <c r="BE244" t="n">
         <v>31124486</v>
       </c>
-      <c r="AT244" t="n">
+      <c r="BF244" t="n">
         <v>29088047</v>
       </c>
-      <c r="AU244" t="n">
+      <c r="BG244" t="n">
         <v>27958218</v>
       </c>
-      <c r="AV244" t="n">
+      <c r="BH244" t="n">
         <v>22260817</v>
       </c>
-      <c r="AW244" t="n">
+      <c r="BI244" t="n">
         <v>21734359</v>
       </c>
-      <c r="AX244" t="n">
+      <c r="BJ244" t="n">
         <v>16811787</v>
       </c>
-      <c r="AY244" t="n">
+      <c r="BK244" t="n">
         <v>17891787</v>
       </c>
-      <c r="AZ244" t="n">
+      <c r="BL244" t="n">
         <v>21527315</v>
       </c>
-      <c r="BA244" t="n">
+      <c r="BM244" t="n">
         <v>24147735</v>
       </c>
-      <c r="BB244" t="n">
+      <c r="BN244" t="n">
         <v>28377075</v>
       </c>
-      <c r="BC244" t="n">
+      <c r="BO244" t="n">
         <v>27765911</v>
       </c>
-      <c r="BD244" t="n">
+      <c r="BP244" t="n">
         <v>30082231</v>
       </c>
-      <c r="BE244" t="n">
+      <c r="BQ244" t="n">
         <v>30637538</v>
       </c>
-      <c r="BF244" t="n">
+      <c r="BR244" t="n">
         <v>29010492</v>
       </c>
-      <c r="BG244" t="n">
+      <c r="BS244" t="n">
         <v>28264235</v>
       </c>
-      <c r="BH244" t="n">
+      <c r="BT244" t="n">
         <v>22257252</v>
       </c>
-      <c r="BI244" t="n">
+      <c r="BU244" t="n">
         <v>22439023</v>
       </c>
     </row>
@@ -8010,183 +8751,219 @@
         </is>
       </c>
       <c r="B245" t="n">
+        <v>15968171</v>
+      </c>
+      <c r="C245" t="n">
+        <v>17614205</v>
+      </c>
+      <c r="D245" t="n">
+        <v>8372820</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" t="n">
+        <v>271148</v>
+      </c>
+      <c r="G245" t="n">
+        <v>1870057</v>
+      </c>
+      <c r="H245" t="n">
+        <v>11731245</v>
+      </c>
+      <c r="I245" t="n">
+        <v>16927211</v>
+      </c>
+      <c r="J245" t="n">
+        <v>8219094</v>
+      </c>
+      <c r="K245" t="n">
+        <v>5128825</v>
+      </c>
+      <c r="L245" t="n">
+        <v>2874269</v>
+      </c>
+      <c r="M245" t="n">
+        <v>3245991</v>
+      </c>
+      <c r="N245" t="n">
         <v>2459472</v>
       </c>
-      <c r="C245" t="n">
+      <c r="O245" t="n">
         <v>2384740</v>
       </c>
-      <c r="D245" t="n">
+      <c r="P245" t="n">
         <v>3521657</v>
       </c>
-      <c r="E245" t="n">
+      <c r="Q245" t="n">
         <v>4142415</v>
       </c>
-      <c r="F245" t="n">
+      <c r="R245" t="n">
         <v>7342738</v>
       </c>
-      <c r="G245" t="n">
+      <c r="S245" t="n">
         <v>14259622</v>
       </c>
-      <c r="H245" t="n">
+      <c r="T245" t="n">
         <v>26351353</v>
       </c>
-      <c r="I245" t="n">
+      <c r="U245" t="n">
         <v>34460041</v>
       </c>
-      <c r="J245" t="n">
+      <c r="V245" t="n">
         <v>25679512</v>
       </c>
-      <c r="K245" t="n">
+      <c r="W245" t="n">
         <v>23935219</v>
       </c>
-      <c r="L245" t="n">
+      <c r="X245" t="n">
         <v>14930646</v>
       </c>
-      <c r="M245" t="n">
+      <c r="Y245" t="n">
         <v>13220155</v>
       </c>
-      <c r="N245" t="n">
+      <c r="Z245" t="n">
         <v>10598386</v>
       </c>
-      <c r="O245" t="n">
+      <c r="AA245" t="n">
         <v>13623546</v>
       </c>
-      <c r="P245" t="n">
+      <c r="AB245" t="n">
         <v>17632648</v>
       </c>
-      <c r="Q245" t="n">
+      <c r="AC245" t="n">
         <v>25197638</v>
       </c>
-      <c r="R245" t="n">
+      <c r="AD245" t="n">
         <v>29785395</v>
       </c>
-      <c r="S245" t="n">
+      <c r="AE245" t="n">
         <v>35111326</v>
       </c>
-      <c r="T245" t="n">
+      <c r="AF245" t="n">
         <v>42121775</v>
       </c>
-      <c r="U245" t="n">
+      <c r="AG245" t="n">
         <v>46140100</v>
       </c>
-      <c r="V245" t="n">
+      <c r="AH245" t="n">
         <v>35999862</v>
       </c>
-      <c r="W245" t="n">
+      <c r="AI245" t="n">
         <v>29865924</v>
       </c>
-      <c r="X245" t="n">
+      <c r="AJ245" t="n">
         <v>17661676</v>
       </c>
-      <c r="Y245" t="n">
+      <c r="AK245" t="n">
         <v>16627833</v>
       </c>
-      <c r="Z245" t="n">
+      <c r="AL245" t="n">
         <v>15518650</v>
       </c>
-      <c r="AA245" t="n">
+      <c r="AM245" t="n">
         <v>16816546</v>
       </c>
-      <c r="AB245" t="n">
+      <c r="AN245" t="n">
         <v>20648210</v>
       </c>
-      <c r="AC245" t="n">
+      <c r="AO245" t="n">
         <v>28046753</v>
       </c>
-      <c r="AD245" t="n">
+      <c r="AP245" t="n">
         <v>32187668</v>
       </c>
-      <c r="AE245" t="n">
+      <c r="AQ245" t="n">
         <v>36255025</v>
       </c>
-      <c r="AF245" t="n">
+      <c r="AR245" t="n">
         <v>43109417</v>
       </c>
-      <c r="AG245" t="n">
+      <c r="AS245" t="n">
         <v>46695607</v>
       </c>
-      <c r="AH245" t="n">
+      <c r="AT245" t="n">
         <v>37980229</v>
       </c>
-      <c r="AI245" t="n">
+      <c r="AU245" t="n">
         <v>32415687</v>
       </c>
-      <c r="AJ245" t="n">
+      <c r="AV245" t="n">
         <v>19023828</v>
       </c>
-      <c r="AK245" t="n">
+      <c r="AW245" t="n">
         <v>17913858</v>
       </c>
-      <c r="AL245" t="n">
+      <c r="AX245" t="n">
         <v>16491597</v>
       </c>
-      <c r="AM245" t="n">
+      <c r="AY245" t="n">
         <v>18498127</v>
       </c>
-      <c r="AN245" t="n">
+      <c r="AZ245" t="n">
         <v>24520235</v>
       </c>
-      <c r="AO245" t="n">
+      <c r="BA245" t="n">
         <v>27099375</v>
       </c>
-      <c r="AP245" t="n">
+      <c r="BB245" t="n">
         <v>35701081</v>
       </c>
-      <c r="AQ245" t="n">
+      <c r="BC245" t="n">
         <v>38185200</v>
       </c>
-      <c r="AR245" t="n">
+      <c r="BD245" t="n">
         <v>43918940</v>
       </c>
-      <c r="AS245" t="n">
+      <c r="BE245" t="n">
         <v>47760600</v>
       </c>
-      <c r="AT245" t="n">
+      <c r="BF245" t="n">
         <v>38965938</v>
       </c>
-      <c r="AU245" t="n">
+      <c r="BG245" t="n">
         <v>33836772</v>
       </c>
-      <c r="AV245" t="n">
+      <c r="BH245" t="n">
         <v>19978052</v>
       </c>
-      <c r="AW245" t="n">
+      <c r="BI245" t="n">
         <v>18025525</v>
       </c>
-      <c r="AX245" t="n">
+      <c r="BJ245" t="n">
         <v>16910798</v>
       </c>
-      <c r="AY245" t="n">
+      <c r="BK245" t="n">
         <v>18412443</v>
       </c>
-      <c r="AZ245" t="n">
+      <c r="BL245" t="n">
         <v>22344695</v>
       </c>
-      <c r="BA245" t="n">
+      <c r="BM245" t="n">
         <v>29070077</v>
       </c>
-      <c r="BB245" t="n">
+      <c r="BN245" t="n">
         <v>35565862</v>
       </c>
-      <c r="BC245" t="n">
+      <c r="BO245" t="n">
         <v>38982683</v>
       </c>
-      <c r="BD245" t="n">
+      <c r="BP245" t="n">
         <v>44691923</v>
       </c>
-      <c r="BE245" t="n">
+      <c r="BQ245" t="n">
         <v>48181913</v>
       </c>
-      <c r="BF245" t="n">
+      <c r="BR245" t="n">
         <v>39420119</v>
       </c>
-      <c r="BG245" t="n">
+      <c r="BS245" t="n">
         <v>34281206</v>
       </c>
-      <c r="BH245" t="n">
+      <c r="BT245" t="n">
         <v>20301411</v>
       </c>
-      <c r="BI245" t="n">
+      <c r="BU245" t="n">
         <v>18546462</v>
       </c>
     </row>
@@ -8197,183 +8974,219 @@
         </is>
       </c>
       <c r="B246" t="n">
+        <v>13566938</v>
+      </c>
+      <c r="C246" t="n">
+        <v>14515965</v>
+      </c>
+      <c r="D246" t="n">
+        <v>7212999</v>
+      </c>
+      <c r="E246" t="n">
+        <v>721353</v>
+      </c>
+      <c r="F246" t="n">
+        <v>1500619</v>
+      </c>
+      <c r="G246" t="n">
+        <v>5939182</v>
+      </c>
+      <c r="H246" t="n">
+        <v>15083194</v>
+      </c>
+      <c r="I246" t="n">
+        <v>18994313</v>
+      </c>
+      <c r="J246" t="n">
+        <v>11882532</v>
+      </c>
+      <c r="K246" t="n">
+        <v>9334974</v>
+      </c>
+      <c r="L246" t="n">
+        <v>3542593</v>
+      </c>
+      <c r="M246" t="n">
+        <v>4578193</v>
+      </c>
+      <c r="N246" t="n">
         <v>4910460</v>
       </c>
-      <c r="C246" t="n">
+      <c r="O246" t="n">
         <v>5170074</v>
       </c>
-      <c r="D246" t="n">
+      <c r="P246" t="n">
         <v>5431070</v>
       </c>
-      <c r="E246" t="n">
+      <c r="Q246" t="n">
         <v>3761860</v>
       </c>
-      <c r="F246" t="n">
+      <c r="R246" t="n">
         <v>7642312</v>
       </c>
-      <c r="G246" t="n">
+      <c r="S246" t="n">
         <v>11733296</v>
       </c>
-      <c r="H246" t="n">
+      <c r="T246" t="n">
         <v>18916313</v>
       </c>
-      <c r="I246" t="n">
+      <c r="U246" t="n">
         <v>21561752</v>
       </c>
-      <c r="J246" t="n">
+      <c r="V246" t="n">
         <v>16673654</v>
       </c>
-      <c r="K246" t="n">
+      <c r="W246" t="n">
         <v>16260855</v>
       </c>
-      <c r="L246" t="n">
+      <c r="X246" t="n">
         <v>12794287</v>
       </c>
-      <c r="M246" t="n">
+      <c r="Y246" t="n">
         <v>12612742</v>
       </c>
-      <c r="N246" t="n">
+      <c r="Z246" t="n">
         <v>9285519</v>
       </c>
-      <c r="O246" t="n">
+      <c r="AA246" t="n">
         <v>11927351</v>
       </c>
-      <c r="P246" t="n">
+      <c r="AB246" t="n">
         <v>14469426</v>
       </c>
-      <c r="Q246" t="n">
+      <c r="AC246" t="n">
         <v>17120921</v>
       </c>
-      <c r="R246" t="n">
+      <c r="AD246" t="n">
         <v>19168893</v>
       </c>
-      <c r="S246" t="n">
+      <c r="AE246" t="n">
         <v>20978588</v>
       </c>
-      <c r="T246" t="n">
+      <c r="AF246" t="n">
         <v>24653224</v>
       </c>
-      <c r="U246" t="n">
+      <c r="AG246" t="n">
         <v>25548662</v>
       </c>
-      <c r="V246" t="n">
+      <c r="AH246" t="n">
         <v>20386845</v>
       </c>
-      <c r="W246" t="n">
+      <c r="AI246" t="n">
         <v>18726455</v>
       </c>
-      <c r="X246" t="n">
+      <c r="AJ246" t="n">
         <v>14242796</v>
       </c>
-      <c r="Y246" t="n">
+      <c r="AK246" t="n">
         <v>15256575</v>
       </c>
-      <c r="Z246" t="n">
+      <c r="AL246" t="n">
         <v>13187513</v>
       </c>
-      <c r="AA246" t="n">
+      <c r="AM246" t="n">
         <v>13888423</v>
       </c>
-      <c r="AB246" t="n">
+      <c r="AN246" t="n">
         <v>15461699</v>
       </c>
-      <c r="AC246" t="n">
+      <c r="AO246" t="n">
         <v>18542404</v>
       </c>
-      <c r="AD246" t="n">
+      <c r="AP246" t="n">
         <v>20230336</v>
       </c>
-      <c r="AE246" t="n">
+      <c r="AQ246" t="n">
         <v>21277136</v>
       </c>
-      <c r="AF246" t="n">
+      <c r="AR246" t="n">
         <v>23316073</v>
       </c>
-      <c r="AG246" t="n">
+      <c r="AS246" t="n">
         <v>24138434</v>
       </c>
-      <c r="AH246" t="n">
+      <c r="AT246" t="n">
         <v>20743366</v>
       </c>
-      <c r="AI246" t="n">
+      <c r="AU246" t="n">
         <v>18047994</v>
       </c>
-      <c r="AJ246" t="n">
+      <c r="AV246" t="n">
         <v>13841344</v>
       </c>
-      <c r="AK246" t="n">
+      <c r="AW246" t="n">
         <v>14754653</v>
       </c>
-      <c r="AL246" t="n">
+      <c r="AX246" t="n">
         <v>12855490</v>
       </c>
-      <c r="AM246" t="n">
+      <c r="AY246" t="n">
         <v>13650663</v>
       </c>
-      <c r="AN246" t="n">
+      <c r="AZ246" t="n">
         <v>16523807</v>
       </c>
-      <c r="AO246" t="n">
+      <c r="BA246" t="n">
         <v>16891213</v>
       </c>
-      <c r="AP246" t="n">
+      <c r="BB246" t="n">
         <v>20136254</v>
       </c>
-      <c r="AQ246" t="n">
+      <c r="BC246" t="n">
         <v>20285444</v>
       </c>
-      <c r="AR246" t="n">
+      <c r="BD246" t="n">
         <v>21892288</v>
       </c>
-      <c r="AS246" t="n">
+      <c r="BE246" t="n">
         <v>24314153</v>
       </c>
-      <c r="AT246" t="n">
+      <c r="BF246" t="n">
         <v>20160828</v>
       </c>
-      <c r="AU246" t="n">
+      <c r="BG246" t="n">
         <v>18281385</v>
       </c>
-      <c r="AV246" t="n">
+      <c r="BH246" t="n">
         <v>14411484</v>
       </c>
-      <c r="AW246" t="n">
+      <c r="BI246" t="n">
         <v>15059467</v>
       </c>
-      <c r="AX246" t="n">
+      <c r="BJ246" t="n">
         <v>13092929</v>
       </c>
-      <c r="AY246" t="n">
+      <c r="BK246" t="n">
         <v>13601414</v>
       </c>
-      <c r="AZ246" t="n">
+      <c r="BL246" t="n">
         <v>15378087</v>
       </c>
-      <c r="BA246" t="n">
+      <c r="BM246" t="n">
         <v>18493968</v>
       </c>
-      <c r="BB246" t="n">
+      <c r="BN246" t="n">
         <v>20245801</v>
       </c>
-      <c r="BC246" t="n">
+      <c r="BO246" t="n">
         <v>21483797</v>
       </c>
-      <c r="BD246" t="n">
+      <c r="BP246" t="n">
         <v>23537313</v>
       </c>
-      <c r="BE246" t="n">
+      <c r="BQ246" t="n">
         <v>25176511</v>
       </c>
-      <c r="BF246" t="n">
+      <c r="BR246" t="n">
         <v>20444876</v>
       </c>
-      <c r="BG246" t="n">
+      <c r="BS246" t="n">
         <v>18827893</v>
       </c>
-      <c r="BH246" t="n">
+      <c r="BT246" t="n">
         <v>14131248</v>
       </c>
-      <c r="BI246" t="n">
+      <c r="BU246" t="n">
         <v>15784733</v>
       </c>
     </row>
@@ -8396,30 +9209,33 @@
         </is>
       </c>
       <c r="C252" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D252" t="n">
         <v>2016</v>
       </c>
-      <c r="D252" t="n">
+      <c r="E252" t="n">
         <v>2017</v>
       </c>
-      <c r="E252" t="n">
+      <c r="F252" t="n">
         <v>2018</v>
       </c>
-      <c r="F252" t="n">
+      <c r="G252" t="n">
         <v>2019</v>
       </c>
-      <c r="G252" t="n">
+      <c r="H252" t="n">
         <v>2020</v>
       </c>
-      <c r="H252" t="n">
+      <c r="I252" t="n">
         <v>2021</v>
       </c>
-      <c r="I252" t="n">
+      <c r="J252" t="n">
         <v>2022</v>
       </c>
-      <c r="J252" t="n">
+      <c r="K252" t="n">
         <v>2023</v>
       </c>
-      <c r="K252" t="n">
+      <c r="L252" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -8435,30 +9251,33 @@
         </is>
       </c>
       <c r="C253" t="n">
+        <v>210083293</v>
+      </c>
+      <c r="D253" t="n">
         <v>213495421</v>
       </c>
-      <c r="D253" t="n">
+      <c r="E253" t="n">
         <v>202296144</v>
       </c>
-      <c r="E253" t="n">
+      <c r="F253" t="n">
         <v>225708302</v>
       </c>
-      <c r="F253" t="n">
+      <c r="G253" t="n">
         <v>219584535</v>
       </c>
-      <c r="G253" t="n">
+      <c r="H253" t="n">
         <v>126363886</v>
       </c>
-      <c r="H253" t="n">
+      <c r="I253" t="n">
         <v>156531167</v>
       </c>
-      <c r="I253" t="n">
+      <c r="J253" t="n">
         <v>191695483</v>
       </c>
-      <c r="J253" t="n">
+      <c r="K253" t="n">
         <v>216368017</v>
       </c>
-      <c r="K253" t="n">
+      <c r="L253" t="n">
         <v>240157324</v>
       </c>
     </row>
@@ -8474,30 +9293,33 @@
         </is>
       </c>
       <c r="C254" t="n">
+        <v>37792654</v>
+      </c>
+      <c r="D254" t="n">
         <v>42152657</v>
       </c>
-      <c r="D254" t="n">
+      <c r="E254" t="n">
         <v>41280965</v>
       </c>
-      <c r="E254" t="n">
+      <c r="F254" t="n">
         <v>42170810</v>
       </c>
-      <c r="F254" t="n">
+      <c r="G254" t="n">
         <v>40933351</v>
       </c>
-      <c r="G254" t="n">
+      <c r="H254" t="n">
         <v>19798527</v>
       </c>
-      <c r="H254" t="n">
+      <c r="I254" t="n">
         <v>21627122</v>
       </c>
-      <c r="I254" t="n">
+      <c r="J254" t="n">
         <v>29996240</v>
       </c>
-      <c r="J254" t="n">
+      <c r="K254" t="n">
         <v>34276919</v>
       </c>
-      <c r="K254" t="n">
+      <c r="L254" t="n">
         <v>36998211</v>
       </c>
     </row>
@@ -8513,30 +9335,33 @@
         </is>
       </c>
       <c r="C255" t="n">
+        <v>129381060</v>
+      </c>
+      <c r="D255" t="n">
         <v>136718002</v>
       </c>
-      <c r="D255" t="n">
+      <c r="E255" t="n">
         <v>144731444</v>
       </c>
-      <c r="E255" t="n">
+      <c r="F255" t="n">
         <v>146661580</v>
       </c>
-      <c r="F255" t="n">
+      <c r="G255" t="n">
         <v>145713398</v>
       </c>
-      <c r="G255" t="n">
+      <c r="H255" t="n">
         <v>76102977</v>
       </c>
-      <c r="H255" t="n">
+      <c r="I255" t="n">
         <v>109029569</v>
       </c>
-      <c r="I255" t="n">
+      <c r="J255" t="n">
         <v>131651380</v>
       </c>
-      <c r="J255" t="n">
+      <c r="K255" t="n">
         <v>138318957</v>
       </c>
-      <c r="K255" t="n">
+      <c r="L255" t="n">
         <v>140856393</v>
       </c>
     </row>
@@ -8552,30 +9377,33 @@
         </is>
       </c>
       <c r="C256" t="n">
+        <v>7030098</v>
+      </c>
+      <c r="D256" t="n">
         <v>8755302</v>
       </c>
-      <c r="D256" t="n">
+      <c r="E256" t="n">
         <v>7976367</v>
       </c>
-      <c r="E256" t="n">
+      <c r="F256" t="n">
         <v>8628594</v>
       </c>
-      <c r="F256" t="n">
+      <c r="G256" t="n">
         <v>8603210</v>
       </c>
-      <c r="G256" t="n">
+      <c r="H256" t="n">
         <v>2961162</v>
       </c>
-      <c r="H256" t="n">
+      <c r="I256" t="n">
         <v>4729230</v>
       </c>
-      <c r="I256" t="n">
+      <c r="J256" t="n">
         <v>6540212</v>
       </c>
-      <c r="J256" t="n">
+      <c r="K256" t="n">
         <v>8501236</v>
       </c>
-      <c r="K256" t="n">
+      <c r="L256" t="n">
         <v>8633432</v>
       </c>
     </row>
@@ -8591,30 +9419,33 @@
         </is>
       </c>
       <c r="C257" t="n">
+        <v>183110642</v>
+      </c>
+      <c r="D257" t="n">
         <v>179613679</v>
       </c>
-      <c r="D257" t="n">
+      <c r="E257" t="n">
         <v>196173554</v>
       </c>
-      <c r="E257" t="n">
+      <c r="F257" t="n">
         <v>196114914</v>
       </c>
-      <c r="F257" t="n">
+      <c r="G257" t="n">
         <v>193354601</v>
       </c>
-      <c r="G257" t="n">
+      <c r="H257" t="n">
         <v>147988211</v>
       </c>
-      <c r="H257" t="n">
+      <c r="I257" t="n">
         <v>181771179</v>
       </c>
-      <c r="I257" t="n">
+      <c r="J257" t="n">
         <v>206169571</v>
       </c>
-      <c r="J257" t="n">
+      <c r="K257" t="n">
         <v>217636261</v>
       </c>
-      <c r="K257" t="n">
+      <c r="L257" t="n">
         <v>206484954</v>
       </c>
     </row>
@@ -8630,30 +9461,33 @@
         </is>
       </c>
       <c r="C258" t="n">
+        <v>16046025</v>
+      </c>
+      <c r="D258" t="n">
         <v>16396747</v>
       </c>
-      <c r="D258" t="n">
+      <c r="E258" t="n">
         <v>24601255</v>
       </c>
-      <c r="E258" t="n">
+      <c r="F258" t="n">
         <v>24114998</v>
       </c>
-      <c r="F258" t="n">
+      <c r="G258" t="n">
         <v>23213551</v>
       </c>
-      <c r="G258" t="n">
+      <c r="H258" t="n">
         <v>15433495</v>
       </c>
-      <c r="H258" t="n">
+      <c r="I258" t="n">
         <v>18564784</v>
       </c>
-      <c r="I258" t="n">
+      <c r="J258" t="n">
         <v>23096113</v>
       </c>
-      <c r="J258" t="n">
+      <c r="K258" t="n">
         <v>21821377</v>
       </c>
-      <c r="K258" t="n">
+      <c r="L258" t="n">
         <v>33275982</v>
       </c>
     </row>

--- a/outputs/views_single_sheet.xlsx
+++ b/outputs/views_single_sheet.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="demographics" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="tourism" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="economics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9494,4 +9495,1823 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BI60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>consumer_confidence_index</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>99.66687</v>
+      </c>
+      <c r="C4" t="n">
+        <v>99.80013</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100.0481</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100.2951</v>
+      </c>
+      <c r="F4" t="n">
+        <v>100.6629</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100.9915</v>
+      </c>
+      <c r="H4" t="n">
+        <v>101.1128</v>
+      </c>
+      <c r="I4" t="n">
+        <v>101.1448</v>
+      </c>
+      <c r="J4" t="n">
+        <v>101.1952</v>
+      </c>
+      <c r="K4" t="n">
+        <v>101.0767</v>
+      </c>
+      <c r="L4" t="n">
+        <v>100.8589</v>
+      </c>
+      <c r="M4" t="n">
+        <v>100.6374</v>
+      </c>
+      <c r="N4" t="n">
+        <v>100.4013</v>
+      </c>
+      <c r="O4" t="n">
+        <v>99.86548999999999</v>
+      </c>
+      <c r="P4" t="n">
+        <v>98.99875</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>98.28712</v>
+      </c>
+      <c r="R4" t="n">
+        <v>97.83069999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>97.43286000000001</v>
+      </c>
+      <c r="T4" t="n">
+        <v>97.01776</v>
+      </c>
+      <c r="U4" t="n">
+        <v>96.71699</v>
+      </c>
+      <c r="V4" t="n">
+        <v>96.46775</v>
+      </c>
+      <c r="W4" t="n">
+        <v>96.52760000000001</v>
+      </c>
+      <c r="X4" t="n">
+        <v>96.84836</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>97.28867</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>97.74052</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>98.13628</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>98.40537</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>98.68143000000001</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>98.83868</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>98.87727</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>98.84372999999999</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>98.75355</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>98.66359</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>98.60666000000001</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>98.58423999999999</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>98.64285</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>98.68248</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>98.88435</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>99.14597000000001</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>99.42401</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>99.58932</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>99.69349</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>99.76466000000001</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>99.72279</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>99.67807000000001</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>99.681</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>99.61151</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>99.54563</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>99.47481999999999</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>99.46912</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>99.53403</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>99.61620000000001</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>99.71351</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>99.75409999999999</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>99.77131</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>99.72692000000001</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>99.68848</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>99.58195000000001</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>99.50239999999999</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>99.52884</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>97.70017</v>
+      </c>
+      <c r="C5" t="n">
+        <v>98.22165</v>
+      </c>
+      <c r="D5" t="n">
+        <v>99.18996</v>
+      </c>
+      <c r="E5" t="n">
+        <v>99.98609</v>
+      </c>
+      <c r="F5" t="n">
+        <v>100.5841</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100.9527</v>
+      </c>
+      <c r="H5" t="n">
+        <v>101.1354</v>
+      </c>
+      <c r="I5" t="n">
+        <v>101.1922</v>
+      </c>
+      <c r="J5" t="n">
+        <v>101.0743</v>
+      </c>
+      <c r="K5" t="n">
+        <v>100.764</v>
+      </c>
+      <c r="L5" t="n">
+        <v>100.1675</v>
+      </c>
+      <c r="M5" t="n">
+        <v>99.84808</v>
+      </c>
+      <c r="N5" t="n">
+        <v>99.56116</v>
+      </c>
+      <c r="O5" t="n">
+        <v>98.77092</v>
+      </c>
+      <c r="P5" t="n">
+        <v>97.1917</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>96.34094</v>
+      </c>
+      <c r="R5" t="n">
+        <v>95.89206</v>
+      </c>
+      <c r="S5" t="n">
+        <v>95.11839999999999</v>
+      </c>
+      <c r="T5" t="n">
+        <v>94.38748</v>
+      </c>
+      <c r="U5" t="n">
+        <v>94.29604</v>
+      </c>
+      <c r="V5" t="n">
+        <v>94.5082</v>
+      </c>
+      <c r="W5" t="n">
+        <v>95.00515</v>
+      </c>
+      <c r="X5" t="n">
+        <v>95.73175000000001</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>96.46687</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>97.029</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>97.30398</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>97.41732</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>97.79828999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>98.30374</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>98.96724</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>99.35232000000001</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>99.04723</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>98.43823</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>98.13882</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>98.10148</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>98.22784</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>98.43429</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>98.77981</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>99.14660000000001</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>99.43129</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>99.57366</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>99.63921000000001</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>99.67677</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>99.70948</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>99.92326</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>100.1255</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>100.3225</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>100.4038</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>100.2281</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>99.88108</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>99.51148999999999</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>99.22671</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>99.17956</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>99.14695</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>99.17019000000001</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>99.41817</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>99.74033</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>99.92717</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>99.89664</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>99.76157000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>98.85334</v>
+      </c>
+      <c r="C6" t="n">
+        <v>99.05428000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>99.56672</v>
+      </c>
+      <c r="E6" t="n">
+        <v>100.1922</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100.9601</v>
+      </c>
+      <c r="G6" t="n">
+        <v>101.5277</v>
+      </c>
+      <c r="H6" t="n">
+        <v>101.516</v>
+      </c>
+      <c r="I6" t="n">
+        <v>101.277</v>
+      </c>
+      <c r="J6" t="n">
+        <v>101.1606</v>
+      </c>
+      <c r="K6" t="n">
+        <v>100.8813</v>
+      </c>
+      <c r="L6" t="n">
+        <v>100.5841</v>
+      </c>
+      <c r="M6" t="n">
+        <v>100.2511</v>
+      </c>
+      <c r="N6" t="n">
+        <v>99.81926</v>
+      </c>
+      <c r="O6" t="n">
+        <v>99.10256</v>
+      </c>
+      <c r="P6" t="n">
+        <v>97.99290000000001</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>97.40778</v>
+      </c>
+      <c r="R6" t="n">
+        <v>97.14031</v>
+      </c>
+      <c r="S6" t="n">
+        <v>96.95766</v>
+      </c>
+      <c r="T6" t="n">
+        <v>96.91983999999999</v>
+      </c>
+      <c r="U6" t="n">
+        <v>96.99772</v>
+      </c>
+      <c r="V6" t="n">
+        <v>96.95685</v>
+      </c>
+      <c r="W6" t="n">
+        <v>97.04956</v>
+      </c>
+      <c r="X6" t="n">
+        <v>97.1575</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>97.08394</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>96.98483</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>96.95466999999999</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>97.12567</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>97.49252</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>97.94678</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>98.34627</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>98.52292</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>98.47356000000001</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>98.36293000000001</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>98.39339</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>98.6589</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>98.88348000000001</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>98.97713</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>98.83687999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>98.71513</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>98.5899</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>98.59456</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>98.6041</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>98.69248</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>98.9177</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>99.02813</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>98.85326000000001</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>98.52699</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>98.35442</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>98.52218999999999</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>98.62938</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>98.46934</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>98.17923</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>97.93805999999999</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>97.82043</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>97.75543</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>97.66985</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>97.73289</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>98.00545</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>98.17167999999999</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>98.24182</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gdp_current_prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3535.812</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3764.023</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4057.272</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3960.332</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3938.244</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4358.147</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4204.327</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4563.523</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4684.182</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5013.574</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1242.673</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1321.288</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1432.292</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1403.651</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1288.751</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1462.216</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1449.99</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1619.949</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1725.152</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1891.371</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2469.726</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2587.955</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2782.838</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2723.094</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2645.806</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2968.405</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2796.987</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3061.093</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3160.902</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3361.557</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gdp_per_capita_current_prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2027</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2028</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2029</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>43189.577</v>
+      </c>
+      <c r="C22" t="n">
+        <v>45881.456</v>
+      </c>
+      <c r="D22" t="n">
+        <v>49384.527</v>
+      </c>
+      <c r="E22" t="n">
+        <v>48177.607</v>
+      </c>
+      <c r="F22" t="n">
+        <v>47953.683</v>
+      </c>
+      <c r="G22" t="n">
+        <v>53151.541</v>
+      </c>
+      <c r="H22" t="n">
+        <v>50943.628</v>
+      </c>
+      <c r="I22" t="n">
+        <v>54793.074</v>
+      </c>
+      <c r="J22" t="n">
+        <v>56086.903</v>
+      </c>
+      <c r="K22" t="n">
+        <v>59925.317</v>
+      </c>
+      <c r="L22" t="n">
+        <v>63599.502</v>
+      </c>
+      <c r="M22" t="n">
+        <v>65580.908</v>
+      </c>
+      <c r="N22" t="n">
+        <v>67653.54300000001</v>
+      </c>
+      <c r="O22" t="n">
+        <v>69713.379</v>
+      </c>
+      <c r="P22" t="n">
+        <v>71683.47500000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>26725.642</v>
+      </c>
+      <c r="C23" t="n">
+        <v>28326.416</v>
+      </c>
+      <c r="D23" t="n">
+        <v>30526.94</v>
+      </c>
+      <c r="E23" t="n">
+        <v>29664.183</v>
+      </c>
+      <c r="F23" t="n">
+        <v>27188.392</v>
+      </c>
+      <c r="G23" t="n">
+        <v>30792.106</v>
+      </c>
+      <c r="H23" t="n">
+        <v>30154.509</v>
+      </c>
+      <c r="I23" t="n">
+        <v>33312.918</v>
+      </c>
+      <c r="J23" t="n">
+        <v>35151.242</v>
+      </c>
+      <c r="K23" t="n">
+        <v>38039.876</v>
+      </c>
+      <c r="L23" t="n">
+        <v>40581.506</v>
+      </c>
+      <c r="M23" t="n">
+        <v>41888.427</v>
+      </c>
+      <c r="N23" t="n">
+        <v>43059.815</v>
+      </c>
+      <c r="O23" t="n">
+        <v>44363.981</v>
+      </c>
+      <c r="P23" t="n">
+        <v>45765.843</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>37081.496</v>
+      </c>
+      <c r="C24" t="n">
+        <v>38756.651</v>
+      </c>
+      <c r="D24" t="n">
+        <v>41539.756</v>
+      </c>
+      <c r="E24" t="n">
+        <v>40487.302</v>
+      </c>
+      <c r="F24" t="n">
+        <v>39230.928</v>
+      </c>
+      <c r="G24" t="n">
+        <v>43848.345</v>
+      </c>
+      <c r="H24" t="n">
+        <v>41095.77</v>
+      </c>
+      <c r="I24" t="n">
+        <v>44853.761</v>
+      </c>
+      <c r="J24" t="n">
+        <v>46187.295</v>
+      </c>
+      <c r="K24" t="n">
+        <v>48981.965</v>
+      </c>
+      <c r="L24" t="n">
+        <v>51707.603</v>
+      </c>
+      <c r="M24" t="n">
+        <v>53048.574</v>
+      </c>
+      <c r="N24" t="n">
+        <v>54515.019</v>
+      </c>
+      <c r="O24" t="n">
+        <v>56050.844</v>
+      </c>
+      <c r="P24" t="n">
+        <v>57606.464</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>inflation_average_consumer_prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>81.995</v>
+      </c>
+      <c r="C40" t="n">
+        <v>82.529</v>
+      </c>
+      <c r="D40" t="n">
+        <v>83.28700000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>83.517</v>
+      </c>
+      <c r="F40" t="n">
+        <v>83.664</v>
+      </c>
+      <c r="G40" t="n">
+        <v>83.777</v>
+      </c>
+      <c r="H40" t="n">
+        <v>83.845</v>
+      </c>
+      <c r="I40" t="n">
+        <v>83.874</v>
+      </c>
+      <c r="J40" t="n">
+        <v>83.89100000000001</v>
+      </c>
+      <c r="K40" t="n">
+        <v>83.893</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>47.487</v>
+      </c>
+      <c r="C41" t="n">
+        <v>48.085</v>
+      </c>
+      <c r="D41" t="n">
+        <v>48.628</v>
+      </c>
+      <c r="E41" t="n">
+        <v>49.078</v>
+      </c>
+      <c r="F41" t="n">
+        <v>49.721</v>
+      </c>
+      <c r="G41" t="n">
+        <v>50.314</v>
+      </c>
+      <c r="H41" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="I41" t="n">
+        <v>51.294</v>
+      </c>
+      <c r="J41" t="n">
+        <v>51.679</v>
+      </c>
+      <c r="K41" t="n">
+        <v>52.004</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>67.697</v>
+      </c>
+      <c r="C42" t="n">
+        <v>68.06</v>
+      </c>
+      <c r="D42" t="n">
+        <v>68.246</v>
+      </c>
+      <c r="E42" t="n">
+        <v>68.437</v>
+      </c>
+      <c r="F42" t="n">
+        <v>68.628</v>
+      </c>
+      <c r="G42" t="n">
+        <v>68.821</v>
+      </c>
+      <c r="H42" t="n">
+        <v>69.014</v>
+      </c>
+      <c r="I42" t="n">
+        <v>69.20699999999999</v>
+      </c>
+      <c r="J42" t="n">
+        <v>69.401</v>
+      </c>
+      <c r="K42" t="n">
+        <v>69.596</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>real_gdp_growth_percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C50" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C59" t="n">
+        <v>13</v>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F59" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C60" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/views_single_sheet.xlsx
+++ b/outputs/views_single_sheet.xlsx
@@ -9503,7 +9503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI60"/>
+  <dimension ref="A1:BI87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10754,7 +10754,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inflation_average_consumer_prices</t>
+          <t>household_disposable_income</t>
         </is>
       </c>
     </row>
@@ -10765,151 +10765,139 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G30" t="n">
         <v>2021</v>
       </c>
-      <c r="C30" t="n">
+      <c r="H30" t="n">
         <v>2022</v>
       </c>
-      <c r="D30" t="n">
+      <c r="I30" t="n">
         <v>2023</v>
       </c>
-      <c r="E30" t="n">
+      <c r="J30" t="n">
         <v>2024</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2027</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2028</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2029</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2030</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5.5</v>
+        <v>30246.5082874666</v>
       </c>
       <c r="C31" t="n">
-        <v>10.8</v>
+        <v>31570.8974904355</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>33615.1802446285</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5</v>
+        <v>35351.7793839047</v>
       </c>
       <c r="F31" t="n">
-        <v>1.7</v>
+        <v>36071.5163052037</v>
       </c>
       <c r="G31" t="n">
-        <v>1.9</v>
+        <v>37802.9092037468</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>42501.3770918378</v>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>45926.6267519884</v>
       </c>
       <c r="J31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.2</v>
+        <v>47685.3791601533</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6.6</v>
+        <v>21291.8728491478</v>
       </c>
       <c r="C32" t="n">
-        <v>5.5</v>
+        <v>22141.1356335517</v>
       </c>
       <c r="D32" t="n">
-        <v>3.3</v>
+        <v>22663.3314861856</v>
       </c>
       <c r="E32" t="n">
-        <v>2.8</v>
+        <v>24582.9902204603</v>
       </c>
       <c r="F32" t="n">
-        <v>2.1</v>
+        <v>23782.4678049223</v>
       </c>
       <c r="G32" t="n">
-        <v>1.9</v>
+        <v>26175.863403135</v>
       </c>
       <c r="H32" t="n">
-        <v>2.5</v>
+        <v>28726.1264569898</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>33453.2943583124</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2</v>
+        <v>35161.9297398487</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.4</v>
+        <v>24924.9379154554</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>25436.327661389</v>
       </c>
       <c r="D33" t="n">
-        <v>4.2</v>
+        <v>26257.1585330353</v>
       </c>
       <c r="E33" t="n">
-        <v>1.7</v>
+        <v>28146.378960002</v>
       </c>
       <c r="F33" t="n">
-        <v>1.5</v>
+        <v>28877.5207135287</v>
       </c>
       <c r="G33" t="n">
-        <v>1.1</v>
+        <v>30167.6571699568</v>
       </c>
       <c r="H33" t="n">
-        <v>2.5</v>
+        <v>33737.7298976999</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>37582.228371007</v>
       </c>
       <c r="J33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.8</v>
+        <v>39420.8018012013</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>population</t>
+          <t>inflation_average_consumer_prices</t>
         </is>
       </c>
     </row>
@@ -10957,34 +10945,34 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>81.995</v>
+        <v>5.5</v>
       </c>
       <c r="C40" t="n">
-        <v>82.529</v>
+        <v>10.8</v>
       </c>
       <c r="D40" t="n">
-        <v>83.28700000000001</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>83.517</v>
+        <v>2.5</v>
       </c>
       <c r="F40" t="n">
-        <v>83.664</v>
+        <v>1.7</v>
       </c>
       <c r="G40" t="n">
-        <v>83.777</v>
+        <v>1.9</v>
       </c>
       <c r="H40" t="n">
-        <v>83.845</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>83.874</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
-        <v>83.89100000000001</v>
+        <v>2.2</v>
       </c>
       <c r="K40" t="n">
-        <v>83.893</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="41">
@@ -10994,34 +10982,34 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>47.487</v>
+        <v>6.6</v>
       </c>
       <c r="C41" t="n">
-        <v>48.085</v>
+        <v>5.5</v>
       </c>
       <c r="D41" t="n">
-        <v>48.628</v>
+        <v>3.3</v>
       </c>
       <c r="E41" t="n">
-        <v>49.078</v>
+        <v>2.8</v>
       </c>
       <c r="F41" t="n">
-        <v>49.721</v>
+        <v>2.1</v>
       </c>
       <c r="G41" t="n">
-        <v>50.314</v>
+        <v>1.9</v>
       </c>
       <c r="H41" t="n">
-        <v>50.84</v>
+        <v>2.5</v>
       </c>
       <c r="I41" t="n">
-        <v>51.294</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>51.679</v>
+        <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>52.004</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -11031,40 +11019,40 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>67.697</v>
+        <v>3.4</v>
       </c>
       <c r="C42" t="n">
-        <v>68.06</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>68.246</v>
+        <v>4.2</v>
       </c>
       <c r="E42" t="n">
-        <v>68.437</v>
+        <v>1.7</v>
       </c>
       <c r="F42" t="n">
-        <v>68.628</v>
+        <v>1.5</v>
       </c>
       <c r="G42" t="n">
-        <v>68.821</v>
+        <v>1.1</v>
       </c>
       <c r="H42" t="n">
-        <v>69.014</v>
+        <v>2.5</v>
       </c>
       <c r="I42" t="n">
-        <v>69.20699999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
-        <v>69.401</v>
+        <v>2.7</v>
       </c>
       <c r="K42" t="n">
-        <v>69.596</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>real_gdp_growth_percent</t>
+          <t>population</t>
         </is>
       </c>
     </row>
@@ -11112,34 +11100,34 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3.9</v>
+        <v>81.995</v>
       </c>
       <c r="C49" t="n">
-        <v>1.8</v>
+        <v>82.529</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.9</v>
+        <v>83.28700000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.5</v>
+        <v>83.517</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2</v>
+        <v>83.664</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9</v>
+        <v>83.777</v>
       </c>
       <c r="H49" t="n">
-        <v>1.5</v>
+        <v>83.845</v>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>83.874</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>83.89100000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7</v>
+        <v>83.893</v>
       </c>
     </row>
     <row r="50">
@@ -11149,34 +11137,34 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6.7</v>
+        <v>47.487</v>
       </c>
       <c r="C50" t="n">
-        <v>6.4</v>
+        <v>48.085</v>
       </c>
       <c r="D50" t="n">
-        <v>2.5</v>
+        <v>48.628</v>
       </c>
       <c r="E50" t="n">
-        <v>3.5</v>
+        <v>49.078</v>
       </c>
       <c r="F50" t="n">
-        <v>2.9</v>
+        <v>49.721</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>50.314</v>
       </c>
       <c r="H50" t="n">
-        <v>1.7</v>
+        <v>50.84</v>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>51.294</v>
       </c>
       <c r="J50" t="n">
-        <v>1.6</v>
+        <v>51.679</v>
       </c>
       <c r="K50" t="n">
-        <v>1.6</v>
+        <v>52.004</v>
       </c>
     </row>
     <row r="51">
@@ -11186,40 +11174,40 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6.8</v>
+        <v>67.697</v>
       </c>
       <c r="C51" t="n">
-        <v>2.8</v>
+        <v>68.06</v>
       </c>
       <c r="D51" t="n">
-        <v>1.6</v>
+        <v>68.246</v>
       </c>
       <c r="E51" t="n">
-        <v>1.1</v>
+        <v>68.437</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7</v>
+        <v>68.628</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9</v>
+        <v>68.821</v>
       </c>
       <c r="H51" t="n">
-        <v>1.2</v>
+        <v>69.014</v>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>69.20699999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>1.2</v>
+        <v>69.401</v>
       </c>
       <c r="K51" t="n">
-        <v>1.2</v>
+        <v>69.596</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>real_gdp_growth_percent</t>
         </is>
       </c>
     </row>
@@ -11244,6 +11232,21 @@
       <c r="F57" t="n">
         <v>2025</v>
       </c>
+      <c r="G57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2030</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -11252,19 +11255,34 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="C58" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="D58" t="n">
-        <v>3.1</v>
+        <v>-0.9</v>
       </c>
       <c r="E58" t="n">
-        <v>3.4</v>
+        <v>-0.5</v>
       </c>
       <c r="F58" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="59">
@@ -11274,19 +11292,34 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>14.9</v>
+        <v>6.7</v>
       </c>
       <c r="C59" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="D59" t="n">
-        <v>12.2</v>
+        <v>2.5</v>
       </c>
       <c r="E59" t="n">
-        <v>11.3</v>
+        <v>3.5</v>
       </c>
       <c r="F59" t="n">
-        <v>10.8</v>
+        <v>2.9</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="60">
@@ -11296,19 +11329,507 @@
         </is>
       </c>
       <c r="B60" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>unemployment_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C68" t="n">
+        <v>13</v>
+      </c>
+      <c r="D68" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E68" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
         <v>7.9</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C69" t="n">
         <v>7.3</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D69" t="n">
         <v>7.3</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E69" t="n">
         <v>7.4</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F69" t="n">
         <v>7.6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>unemployment_rate_25_74_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L76" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C77" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D77" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E77" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F77" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G77" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H77" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I77" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J77" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>6</v>
+      </c>
+      <c r="C78" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F78" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G78" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H78" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I78" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J78" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K78" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L78" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>unemployment_rate_under_25_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C85" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D85" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E85" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F85" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G85" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H85" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I85" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J85" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K85" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L85" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="C86" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E86" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F86" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G86" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="H86" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I86" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J86" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="L86" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C87" t="n">
+        <v>19</v>
+      </c>
+      <c r="D87" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E87" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H87" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I87" t="n">
+        <v>19</v>
+      </c>
+      <c r="J87" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K87" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L87" t="n">
+        <v>18.1</v>
       </c>
     </row>
   </sheetData>
